--- a/Dane/karty_v1.xlsx
+++ b/Dane/karty_v1.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <workbookPr codeName="Ten_skoroszyt" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a40667ca9a5261e0/Dokumenty/Dokumenty/Gra Walka o Dusze/Symulator/Dane/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="44" documentId="8_{C60639C0-3DC1-46DF-8FF5-DD98044E12E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{70274A1B-E009-4778-B9E0-1EDFE440245E}"/>
+  <xr:revisionPtr revIDLastSave="89" documentId="8_{C60639C0-3DC1-46DF-8FF5-DD98044E12E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FDF2BB4B-088A-4B8C-A50A-91B0457261CB}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1C612D17-AB6F-4FCE-AA6C-1D2201D34FB7}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Arkusz1!$B$1:$U$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Arkusz1!$A$1:$V$98</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="93">
   <si>
     <t>klasa</t>
   </si>
@@ -69,15 +69,9 @@
     <t>P</t>
   </si>
   <si>
-    <t>-K4</t>
-  </si>
-  <si>
     <t>Serafin</t>
   </si>
   <si>
-    <t>-K2</t>
-  </si>
-  <si>
     <t>Chwała Pańska</t>
   </si>
   <si>
@@ -279,9 +273,6 @@
     <t>walka_sila_bonus</t>
   </si>
   <si>
-    <t>6,3</t>
-  </si>
-  <si>
     <t>dodac "jeżeli walczysz z klasą nie większą od twojej"</t>
   </si>
   <si>
@@ -301,24 +292,31 @@
   </si>
   <si>
     <t>+K2</t>
+  </si>
+  <si>
+    <t>zarejestrowana</t>
+  </si>
+  <si>
+    <t>ok</t>
+  </si>
+  <si>
+    <t>brak</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>klasa_wroga&lt;</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="238"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="238"/>
@@ -356,22 +354,28 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF7030A0"/>
+      <color theme="0"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="238"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2E3440"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -379,39 +383,48 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF454545"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF454545"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF454545"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF454545"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="11">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+  <cellXfs count="9">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Normalny" xfId="0" builtinId="0"/>
-    <cellStyle name="Procentowy" xfId="1" builtinId="5"/>
+  <cellStyles count="1">
+    <cellStyle name="Normalny" xfId="0" builtinId="0" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -723,105 +736,110 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5603586-01B1-45C3-888E-EC2BF5D85650}">
-  <dimension ref="A1:U39"/>
+  <sheetPr codeName="Arkusz1" filterMode="1"/>
+  <dimension ref="A1:X98"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="15.85546875" style="1" customWidth="1"/>
     <col min="3" max="3" width="9.140625" style="1"/>
     <col min="4" max="5" width="9.140625" style="2"/>
-    <col min="6" max="6" width="24.85546875" style="2" customWidth="1"/>
-    <col min="7" max="7" width="27.7109375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="26" style="2" customWidth="1"/>
-    <col min="9" max="9" width="15.5703125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="19.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="19.42578125" style="6" customWidth="1"/>
-    <col min="12" max="12" width="23.5703125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="19" style="1" customWidth="1"/>
-    <col min="14" max="14" width="9.140625" style="1"/>
-    <col min="15" max="15" width="11" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="18" style="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="6" max="6" width="19.28515625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="24.85546875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="27.7109375" style="2" customWidth="1"/>
+    <col min="9" max="9" width="26" style="2" customWidth="1"/>
+    <col min="10" max="10" width="15.5703125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="19.7109375" style="2" customWidth="1"/>
+    <col min="12" max="12" width="19.42578125" style="5" customWidth="1"/>
+    <col min="13" max="13" width="23.5703125" style="1" customWidth="1"/>
+    <col min="14" max="14" width="19" style="1" customWidth="1"/>
+    <col min="15" max="15" width="9.140625" style="1"/>
+    <col min="16" max="16" width="11" style="2" customWidth="1"/>
+    <col min="17" max="17" width="10.7109375" style="2" customWidth="1"/>
+    <col min="18" max="18" width="10.140625" style="2" customWidth="1"/>
+    <col min="19" max="19" width="14.7109375" style="2" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="2" customWidth="1"/>
+    <col min="21" max="21" width="12.5703125" style="1" customWidth="1"/>
+    <col min="22" max="22" width="18" style="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="H1" s="2" t="s">
+      <c r="F1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="I1" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>88</v>
+      <c r="I1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="M1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="O1" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>52</v>
       </c>
       <c r="P1" s="2" t="s">
         <v>50</v>
       </c>
       <c r="Q1" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="R1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="R1" s="2" t="s">
-        <v>68</v>
-      </c>
       <c r="S1" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>51</v>
+        <v>66</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>52</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>4</v>
       </c>
       <c r="D2" s="2">
@@ -830,34 +848,40 @@
       <c r="E2" s="2">
         <v>1</v>
       </c>
-      <c r="I2" s="2"/>
-      <c r="K2" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="L2" s="8" t="s">
+      <c r="F2" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="J2" s="2"/>
+      <c r="L2" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q2" s="2">
+      <c r="N2" s="8"/>
+      <c r="O2" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="R2" s="2">
         <v>0</v>
       </c>
-      <c r="T2" s="1" t="s">
+      <c r="U2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="U2" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
+      <c r="V2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="W2" s="2"/>
+      <c r="X2" s="2"/>
+    </row>
+    <row r="3" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="2" t="s">
         <v>4</v>
       </c>
       <c r="D3" s="2">
@@ -866,37 +890,43 @@
       <c r="E3" s="2">
         <v>2</v>
       </c>
-      <c r="I3" s="2"/>
-      <c r="K3" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="L3" s="8" t="s">
+      <c r="F3" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="J3" s="2"/>
+      <c r="L3" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="M3" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="N3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q3" s="2">
+      <c r="N3" s="8"/>
+      <c r="O3" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="R3" s="2">
         <v>0</v>
       </c>
-      <c r="S3" s="2">
+      <c r="T3" s="2">
         <v>-1</v>
       </c>
-      <c r="T3" s="1" t="s">
+      <c r="U3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="U3" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
+      <c r="V3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="W3" s="2"/>
+      <c r="X3" s="2"/>
+    </row>
+    <row r="4" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="2" t="s">
         <v>4</v>
       </c>
       <c r="D4" s="2">
@@ -905,41 +935,45 @@
       <c r="E4" s="2">
         <v>3</v>
       </c>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="O4" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q4" s="2">
+      <c r="F4" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="N4" s="8"/>
+      <c r="O4" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="R4" s="2">
         <v>0</v>
       </c>
-      <c r="R4" s="2">
+      <c r="S4" s="2">
         <v>2</v>
       </c>
-      <c r="T4" s="1" t="s">
+      <c r="U4" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
+      <c r="V4" s="2"/>
+      <c r="W4" s="2"/>
+      <c r="X4" s="2"/>
+    </row>
+    <row r="5" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="D5" s="2">
@@ -949,71 +983,84 @@
         <v>4</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I5" s="2"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="N5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q5" s="2" t="s">
-        <v>29</v>
+        <v>90</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="J5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="N5" s="8"/>
+      <c r="O5" s="8" t="s">
+        <v>8</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="T5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="S5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="U5" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
+      <c r="V5" s="2"/>
+      <c r="W5" s="2"/>
+      <c r="X5" s="2"/>
+    </row>
+    <row r="6" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="2" t="s">
         <v>4</v>
       </c>
       <c r="D6" s="2">
         <v>1</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I6" s="2"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q6" s="2">
+        <v>15</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="J6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="N6" s="8"/>
+      <c r="O6" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="R6" s="2">
         <v>0</v>
       </c>
-      <c r="R6" s="2">
-        <v>1</v>
-      </c>
-      <c r="T6" s="1" t="s">
+      <c r="S6" s="2">
+        <v>1</v>
+      </c>
+      <c r="U6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="U6" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
+      <c r="V6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="W6" s="2"/>
+      <c r="X6" s="2"/>
+    </row>
+    <row r="7" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
         <v>6</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="2" t="s">
         <v>4</v>
       </c>
       <c r="D7" s="2">
@@ -1022,43 +1069,48 @@
       <c r="E7" s="2">
         <v>5</v>
       </c>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="K7" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="L7" s="8" t="s">
+      <c r="F7" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="M7" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="M7" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="N7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q7" s="2" t="s">
-        <v>56</v>
+      <c r="N7" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="O7" s="8" t="s">
+        <v>8</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="T7" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="S7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="U7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="U7" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
+      <c r="V7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="W7" s="2"/>
+      <c r="X7" s="2"/>
+    </row>
+    <row r="8" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
         <v>7</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="2" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="2">
@@ -1067,40 +1119,46 @@
       <c r="E8" s="2">
         <v>5</v>
       </c>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K8" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L8" s="1" t="s">
+      <c r="F8" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="M8" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="M8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q8" s="2">
+      <c r="N8" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="O8" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="R8" s="2">
         <v>0</v>
       </c>
-      <c r="R8" s="2">
-        <v>1</v>
-      </c>
-      <c r="T8" s="1" t="s">
+      <c r="S8" s="2">
+        <v>1</v>
+      </c>
+      <c r="U8" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
-        <v>8</v>
-      </c>
-      <c r="B9" s="1" t="s">
+      <c r="V8" s="2"/>
+      <c r="W8" s="2"/>
+      <c r="X8" s="2"/>
+    </row>
+    <row r="9" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="2" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="2">
@@ -1109,46 +1167,51 @@
       <c r="E9" s="2">
         <v>6</v>
       </c>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="K9" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="L9" s="1" t="s">
+      <c r="F9" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M9" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="M9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="O9" s="2">
+      <c r="N9" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="O9" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="P9" s="2">
         <v>-1</v>
       </c>
-      <c r="Q9" s="2">
+      <c r="R9" s="2">
         <v>0</v>
       </c>
-      <c r="R9" s="2">
-        <v>1</v>
-      </c>
-      <c r="T9" s="1" t="s">
+      <c r="S9" s="2">
+        <v>1</v>
+      </c>
+      <c r="U9" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="U9" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
+      <c r="V9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="W9" s="2"/>
+      <c r="X9" s="2"/>
+    </row>
+    <row r="10" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
         <v>9</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="2" t="s">
         <v>4</v>
       </c>
       <c r="D10" s="2">
@@ -1157,48 +1220,53 @@
       <c r="E10" s="2">
         <v>7</v>
       </c>
-      <c r="I10" s="2" t="s">
-        <v>29</v>
+      <c r="F10" s="2" t="s">
+        <v>89</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="K10" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="L10" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="M10" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="M10" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="N10" s="1" t="s">
+      <c r="N10" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="O10" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="O10" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q10" s="2">
-        <v>1</v>
+      <c r="P10" s="2" t="s">
+        <v>56</v>
       </c>
       <c r="R10" s="2">
+        <v>1</v>
+      </c>
+      <c r="S10" s="2">
         <v>2</v>
       </c>
-      <c r="T10" s="1" t="s">
+      <c r="U10" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="U10" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
+      <c r="V10" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="W10" s="2"/>
+      <c r="X10" s="2"/>
+    </row>
+    <row r="11" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
         <v>10</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="2" t="s">
         <v>4</v>
       </c>
       <c r="D11" s="2">
@@ -1207,38 +1275,47 @@
       <c r="E11" s="2">
         <v>8</v>
       </c>
-      <c r="I11" s="2"/>
-      <c r="K11" s="7"/>
-      <c r="L11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="N11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="O11" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="Q11" s="2">
-        <v>1</v>
+      <c r="F11" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="J11" s="2"/>
+      <c r="L11" s="2"/>
+      <c r="M11" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="N11" s="8"/>
+      <c r="O11" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="P11" s="4" t="s">
+        <v>55</v>
       </c>
       <c r="R11" s="2">
+        <v>1</v>
+      </c>
+      <c r="S11" s="2">
         <v>2</v>
       </c>
-      <c r="T11" s="1" t="s">
+      <c r="U11" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="U11" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
+      <c r="V11" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="W11" s="2"/>
+      <c r="X11" s="2"/>
+    </row>
+    <row r="12" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
         <v>11</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C12" s="1" t="s">
+      <c r="B12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>4</v>
       </c>
       <c r="D12" s="2">
@@ -1248,45 +1325,50 @@
         <v>9</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="K12" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="L12" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="J12" s="2"/>
+      <c r="K12" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="M12" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="M12" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N12" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q12" s="2">
+      <c r="N12" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="O12" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="2">
         <v>0</v>
       </c>
-      <c r="S12" s="2">
-        <v>1</v>
-      </c>
-      <c r="T12" s="1" t="s">
+      <c r="T12" s="2">
+        <v>1</v>
+      </c>
+      <c r="U12" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="U12" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
+      <c r="V12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="W12" s="2"/>
+      <c r="X12" s="2"/>
+    </row>
+    <row r="13" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
         <v>12</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C13" s="1" t="s">
+      <c r="B13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>4</v>
       </c>
       <c r="D13" s="2">
@@ -1295,37 +1377,42 @@
       <c r="E13" s="2">
         <v>10</v>
       </c>
-      <c r="G13" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6"/>
-      <c r="J13" s="6"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="N13" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q13" s="2">
+      <c r="F13" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J13" s="2"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="N13" s="8"/>
+      <c r="O13" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="R13" s="2">
         <v>0</v>
       </c>
-      <c r="R13" s="2">
-        <v>1</v>
-      </c>
-      <c r="T13" s="1" t="s">
+      <c r="S13" s="2">
+        <v>1</v>
+      </c>
+      <c r="U13" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A14" s="1">
+      <c r="V13" s="2"/>
+      <c r="W13" s="2"/>
+      <c r="X13" s="2"/>
+    </row>
+    <row r="14" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
         <v>13</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C14" s="1" t="s">
+      <c r="B14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>4</v>
       </c>
       <c r="D14" s="2">
@@ -1335,42 +1422,48 @@
         <v>11</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="K14" s="7"/>
-      <c r="L14" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="N14" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L14" s="2"/>
+      <c r="M14" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="N14" s="8"/>
+      <c r="O14" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="P14" s="2">
+      <c r="Q14" s="2">
         <v>-3</v>
       </c>
-      <c r="Q14" s="2" t="s">
-        <v>25</v>
-      </c>
       <c r="R14" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="T14" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="S14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="U14" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="U14" s="8" t="s">
+      <c r="V14" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="W14" s="2"/>
+      <c r="X14" s="2"/>
+    </row>
+    <row r="15" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A15" s="1">
-        <v>14</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" s="2" t="s">
         <v>4</v>
       </c>
       <c r="D15" s="2">
@@ -1379,35 +1472,41 @@
       <c r="E15" s="2">
         <v>12</v>
       </c>
-      <c r="I15" s="2"/>
-      <c r="K15" s="7"/>
-      <c r="L15" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="N15" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q15" s="2">
+      <c r="F15" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="J15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="N15" s="8"/>
+      <c r="O15" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="R15" s="2">
         <v>0</v>
       </c>
-      <c r="R15" s="2">
-        <v>1</v>
-      </c>
-      <c r="T15" s="1" t="s">
+      <c r="S15" s="2">
+        <v>1</v>
+      </c>
+      <c r="U15" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="U15" s="8" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A16" s="1">
+      <c r="V15" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="W15" s="2"/>
+      <c r="X15" s="2"/>
+    </row>
+    <row r="16" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
         <v>15</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C16" s="1" t="s">
+      <c r="B16" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>4</v>
       </c>
       <c r="D16" s="2">
@@ -1416,47 +1515,43 @@
       <c r="E16" s="2">
         <v>13</v>
       </c>
-      <c r="F16" s="3">
+      <c r="F16" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="J16" s="2"/>
+      <c r="L16" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="M16" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="N16" s="8"/>
+      <c r="O16" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="R16" s="2">
         <v>0</v>
       </c>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="K16" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="L16" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="N16" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q16" s="2">
-        <v>0</v>
-      </c>
-      <c r="S16" s="2">
+      <c r="T16" s="2">
         <v>2</v>
       </c>
-      <c r="T16" s="1" t="s">
+      <c r="U16" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="U16" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A17" s="1">
+      <c r="V16" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="W16" s="2"/>
+      <c r="X16" s="2"/>
+    </row>
+    <row r="17" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
         <v>16</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C17" s="1" t="s">
+      <c r="B17" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>4</v>
       </c>
       <c r="D17" s="2">
@@ -1466,43 +1561,49 @@
         <v>14</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="G17" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="H17" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="H17" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="I17" s="2"/>
-      <c r="K17" s="7"/>
-      <c r="L17" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="N17" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q17" s="2">
+      <c r="I17" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="J17" s="2"/>
+      <c r="L17" s="2"/>
+      <c r="M17" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="N17" s="8"/>
+      <c r="O17" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="R17" s="2">
         <v>0</v>
       </c>
-      <c r="R17" s="2">
-        <v>1</v>
-      </c>
-      <c r="T17" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="U17" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A18" s="1">
+      <c r="S17" s="2">
+        <v>1</v>
+      </c>
+      <c r="U17" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="V17" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="W17" s="2"/>
+      <c r="X17" s="2"/>
+    </row>
+    <row r="18" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
         <v>17</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C18" s="1" t="s">
+      <c r="B18" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>4</v>
       </c>
       <c r="D18" s="2">
@@ -1511,38 +1612,45 @@
       <c r="E18" s="2">
         <v>13</v>
       </c>
-      <c r="G18" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="I18" s="2"/>
-      <c r="K18" s="7"/>
-      <c r="L18" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="N18" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="O18" s="2">
+      <c r="F18" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="J18" s="2"/>
+      <c r="L18" s="2"/>
+      <c r="M18" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="N18" s="8"/>
+      <c r="O18" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="P18" s="2">
         <v>-3</v>
       </c>
-      <c r="Q18" s="2">
+      <c r="R18" s="2">
         <v>0</v>
       </c>
-      <c r="R18" s="2">
-        <v>1</v>
-      </c>
-      <c r="T18" s="1" t="s">
+      <c r="S18" s="2">
+        <v>1</v>
+      </c>
+      <c r="U18" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A19" s="1">
+      <c r="V18" s="2"/>
+      <c r="W18" s="2"/>
+      <c r="X18" s="2"/>
+    </row>
+    <row r="19" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="2">
         <v>18</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19" s="1" t="s">
+      <c r="B19" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>4</v>
       </c>
       <c r="D19" s="2">
@@ -1552,33 +1660,40 @@
         <v>15</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K19" s="7"/>
-      <c r="L19" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="N19" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L19" s="2"/>
+      <c r="M19" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="N19" s="8"/>
+      <c r="O19" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="Q19" s="2">
+      <c r="R19" s="2">
         <v>0</v>
       </c>
-      <c r="T19" s="1" t="s">
+      <c r="U19" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A20" s="1">
+      <c r="V19" s="2"/>
+      <c r="W19" s="2"/>
+      <c r="X19" s="2"/>
+    </row>
+    <row r="20" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
         <v>19</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C20" s="2" t="s">
         <v>4</v>
       </c>
       <c r="D20" s="2">
@@ -1587,33 +1702,40 @@
       <c r="E20" s="2">
         <v>99</v>
       </c>
-      <c r="I20" s="2"/>
-      <c r="K20" s="7"/>
-      <c r="L20" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="N20" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q20" s="2">
+      <c r="F20" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="J20" s="2"/>
+      <c r="L20" s="2"/>
+      <c r="M20" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="N20" s="8"/>
+      <c r="O20" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="R20" s="2">
         <v>0</v>
       </c>
-      <c r="R20" s="2">
-        <v>1</v>
-      </c>
-      <c r="T20" s="1" t="s">
+      <c r="S20" s="2">
+        <v>1</v>
+      </c>
+      <c r="U20" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A21" s="1">
-        <v>1</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>33</v>
+      <c r="V20" s="2"/>
+      <c r="W20" s="2"/>
+      <c r="X20" s="2"/>
+    </row>
+    <row r="21" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2">
+        <v>1</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="D21" s="2">
         <v>1</v>
@@ -1621,37 +1743,41 @@
       <c r="E21" s="2">
         <v>1</v>
       </c>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
-      <c r="K21" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="L21" s="8" t="s">
+      <c r="F21" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="J21" s="2"/>
+      <c r="L21" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M21" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="N21" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q21" s="2">
+      <c r="N21" s="8"/>
+      <c r="O21" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="R21" s="2">
         <v>0</v>
       </c>
-      <c r="T21" s="1" t="s">
+      <c r="U21" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="U21" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A22" s="1">
+      <c r="V21" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="W21" s="2"/>
+      <c r="X21" s="2"/>
+    </row>
+    <row r="22" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2">
         <v>2</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>33</v>
+      <c r="B22" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="D22" s="2">
         <v>1</v>
@@ -1660,42 +1786,50 @@
         <v>2</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H22" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="L22" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="N22" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="O22" s="2">
-        <v>1</v>
-      </c>
-      <c r="Q22" s="2">
+        <v>89</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="J22" s="2"/>
+      <c r="L22" s="2"/>
+      <c r="M22" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="N22" s="8"/>
+      <c r="O22" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="P22" s="2">
         <v>1</v>
       </c>
       <c r="R22" s="2">
         <v>1</v>
       </c>
-      <c r="T22" s="1" t="s">
+      <c r="S22" s="2">
+        <v>1</v>
+      </c>
+      <c r="U22" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="U22" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A23" s="1">
+      <c r="V22" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="W22" s="2"/>
+      <c r="X22" s="2"/>
+    </row>
+    <row r="23" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="2">
         <v>3</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>33</v>
+      <c r="B23" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="D23" s="2">
         <v>1</v>
@@ -1703,40 +1837,46 @@
       <c r="E23" s="2">
         <v>3</v>
       </c>
-      <c r="J23" s="2">
-        <v>1</v>
-      </c>
-      <c r="K23" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="L23" s="8" t="s">
+      <c r="F23" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2">
+        <v>1</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="M23" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="M23" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="N23" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q23" s="2">
+      <c r="N23" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="O23" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="R23" s="2">
         <v>0</v>
       </c>
-      <c r="T23" s="1" t="s">
+      <c r="U23" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="U23" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A24" s="1">
+      <c r="V23" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="W23" s="2"/>
+      <c r="X23" s="2"/>
+    </row>
+    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A24" s="2">
         <v>4</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>33</v>
+      <c r="B24" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="D24" s="2">
         <v>1</v>
@@ -1744,127 +1884,142 @@
       <c r="E24" s="2">
         <v>4</v>
       </c>
-      <c r="I24" s="2"/>
-      <c r="K24" s="6" t="s">
+      <c r="F24" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="L24" s="9" t="s">
+      <c r="J24" s="2"/>
+      <c r="L24" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="M24" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="M24" s="8"/>
-      <c r="N24" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q24" s="2">
+      <c r="N24" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="O24" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="R24" s="2">
         <v>0</v>
       </c>
-      <c r="T24" s="1" t="s">
+      <c r="U24" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="U24" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A25" s="1">
+      <c r="V24" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="W24" s="2"/>
+      <c r="X24" s="2"/>
+    </row>
+    <row r="25" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="2">
         <v>5</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B25" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D25" s="2">
+        <v>1</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J25" s="2"/>
+      <c r="L25" s="2"/>
+      <c r="M25" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="N25" s="8"/>
+      <c r="O25" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="P25" s="2">
+        <v>1</v>
+      </c>
+      <c r="R25" s="2">
+        <v>1</v>
+      </c>
+      <c r="S25" s="2">
+        <v>1</v>
+      </c>
+      <c r="U25" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="V25" s="2"/>
+      <c r="W25" s="2"/>
+      <c r="X25" s="2"/>
+    </row>
+    <row r="26" spans="1:24" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="2">
+        <v>6</v>
+      </c>
+      <c r="B26" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C25" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D25" s="2">
-        <v>1</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G25" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="H25" s="6"/>
-      <c r="I25" s="6"/>
-      <c r="J25" s="6"/>
-      <c r="K25" s="7"/>
-      <c r="L25" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="N25" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="O25" s="2">
-        <v>1</v>
-      </c>
-      <c r="Q25" s="2">
-        <v>1</v>
-      </c>
-      <c r="R25" s="2">
-        <v>1</v>
-      </c>
-      <c r="T25" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="26" spans="1:21" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="8">
-        <v>6</v>
-      </c>
-      <c r="B26" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="D26" s="6">
+      <c r="C26" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D26" s="2">
         <v>2</v>
       </c>
-      <c r="E26" s="6">
+      <c r="E26" s="2">
         <v>5</v>
       </c>
-      <c r="F26" s="6"/>
-      <c r="G26" s="6"/>
-      <c r="H26" s="6"/>
-      <c r="I26" s="6">
-        <v>1</v>
-      </c>
-      <c r="J26" s="6"/>
-      <c r="K26" s="6"/>
-      <c r="L26" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="M26" s="8"/>
-      <c r="N26" s="8" t="s">
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2">
+        <v>1</v>
+      </c>
+      <c r="K26" s="2"/>
+      <c r="L26" s="2"/>
+      <c r="M26" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="N26" s="8"/>
+      <c r="O26" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="O26" s="5">
+      <c r="P26" s="4">
         <v>4</v>
       </c>
-      <c r="P26" s="5"/>
-      <c r="Q26" s="5">
+      <c r="Q26" s="4"/>
+      <c r="R26" s="4">
         <v>2</v>
       </c>
-      <c r="R26" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="S26" s="5"/>
-      <c r="T26" s="9" t="s">
+      <c r="S26" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="T26" s="4"/>
+      <c r="U26" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="U26" s="9" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A27" s="1">
+      <c r="V26" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="W26" s="4"/>
+      <c r="X26" s="4"/>
+    </row>
+    <row r="27" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="2">
         <v>7</v>
       </c>
-      <c r="B27" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>33</v>
+      <c r="B27" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="D27" s="2">
         <v>2</v>
@@ -1873,32 +2028,39 @@
         <v>5</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I27" s="2"/>
-      <c r="K27" s="7"/>
-      <c r="L27" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="N27" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q27" s="2">
+        <v>90</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="J27" s="2"/>
+      <c r="L27" s="2"/>
+      <c r="M27" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="N27" s="8"/>
+      <c r="O27" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="R27" s="2">
         <v>0</v>
       </c>
-      <c r="T27" s="1" t="s">
+      <c r="U27" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A28" s="1">
-        <v>8</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>33</v>
+      <c r="V27" s="2"/>
+      <c r="W27" s="2"/>
+      <c r="X27" s="2"/>
+    </row>
+    <row r="28" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="2">
+        <v>8</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="D28" s="2">
         <v>2</v>
@@ -1906,46 +2068,52 @@
       <c r="E28" s="2">
         <v>6</v>
       </c>
-      <c r="J28" s="2">
+      <c r="F28" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="J28" s="2"/>
+      <c r="K28" s="2">
         <v>3</v>
       </c>
-      <c r="K28" s="6">
-        <v>1</v>
-      </c>
-      <c r="L28" s="1" t="s">
+      <c r="L28" s="2">
+        <v>1</v>
+      </c>
+      <c r="M28" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="M28" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="N28" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="P28" s="2">
-        <v>1</v>
+      <c r="N28" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="O28" s="8" t="s">
+        <v>8</v>
       </c>
       <c r="Q28" s="2">
         <v>1</v>
       </c>
-      <c r="R28" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="T28" s="1" t="s">
+      <c r="R28" s="2">
+        <v>1</v>
+      </c>
+      <c r="S28" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="U28" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="U28" s="8" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A29" s="1">
+      <c r="V28" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="W28" s="2"/>
+      <c r="X28" s="2"/>
+    </row>
+    <row r="29" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="2">
         <v>9</v>
       </c>
-      <c r="B29" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>33</v>
+      <c r="B29" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="D29" s="2">
         <v>2</v>
@@ -1953,43 +2121,50 @@
       <c r="E29" s="2">
         <v>7</v>
       </c>
-      <c r="J29" s="2">
+      <c r="F29" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="J29" s="2"/>
+      <c r="K29" s="2">
         <v>2</v>
       </c>
-      <c r="K29" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="L29" s="8" t="s">
+      <c r="L29" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="M29" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="M29" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="N29" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="P29" s="2" t="s">
-        <v>29</v>
+      <c r="N29" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="O29" s="8" t="s">
+        <v>8</v>
       </c>
       <c r="Q29" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="R29" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="T29" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A30" s="1">
+        <v>27</v>
+      </c>
+      <c r="S29" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="U29" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V29" s="8"/>
+      <c r="W29" s="2"/>
+      <c r="X29" s="2"/>
+    </row>
+    <row r="30" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="2">
         <v>10</v>
       </c>
-      <c r="B30" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="C30" s="8" t="s">
-        <v>33</v>
+      <c r="B30" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="D30" s="2">
         <v>2</v>
@@ -1997,49 +2172,53 @@
       <c r="E30" s="2">
         <v>8</v>
       </c>
-      <c r="F30" s="1"/>
-      <c r="G30" s="1"/>
-      <c r="H30" s="1"/>
-      <c r="J30" s="2">
+      <c r="F30" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="J30" s="2"/>
+      <c r="K30" s="2">
         <v>3.1</v>
       </c>
-      <c r="K30" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="L30" s="8" t="s">
+      <c r="L30" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="M30" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="N30" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="O30" s="2">
-        <v>1</v>
-      </c>
-      <c r="P30" s="2" t="s">
-        <v>63</v>
+      <c r="N30" s="8"/>
+      <c r="O30" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="P30" s="2">
+        <v>1</v>
       </c>
       <c r="Q30" s="2" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="R30" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="T30" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="U30" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A31" s="1">
+        <v>51</v>
+      </c>
+      <c r="S30" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="U30" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="V30" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="W30" s="2"/>
+      <c r="X30" s="2"/>
+    </row>
+    <row r="31" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="2">
         <v>11</v>
       </c>
-      <c r="B31" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>33</v>
+      <c r="B31" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="D31" s="2">
         <v>3</v>
@@ -2047,41 +2226,51 @@
       <c r="E31" s="2">
         <v>9</v>
       </c>
-      <c r="G31" s="6" t="s">
+      <c r="F31" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G31" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="H31" s="6"/>
-      <c r="I31" s="6"/>
-      <c r="J31" s="6"/>
-      <c r="K31" s="7"/>
-      <c r="L31" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="N31" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q31" s="2">
+      <c r="H31" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="J31" s="2"/>
+      <c r="L31" s="2"/>
+      <c r="M31" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="N31" s="8"/>
+      <c r="O31" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="R31" s="2">
         <v>0</v>
       </c>
-      <c r="R31" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="T31" s="1" t="s">
+      <c r="S31" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="U31" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="U31" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A32" s="1">
+      <c r="V31" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="W31" s="2"/>
+      <c r="X31" s="2"/>
+    </row>
+    <row r="32" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="2">
         <v>12</v>
       </c>
-      <c r="B32" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>33</v>
+      <c r="B32" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="D32" s="2">
         <v>3</v>
@@ -2089,48 +2278,51 @@
       <c r="E32" s="2">
         <v>10</v>
       </c>
-      <c r="F32" s="6"/>
-      <c r="G32" s="6"/>
-      <c r="H32" s="6"/>
-      <c r="I32" s="6"/>
-      <c r="J32" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="K32" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="L32" s="8" t="s">
+      <c r="F32" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="J32" s="2"/>
+      <c r="K32" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L32" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="M32" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="M32" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="N32" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="P32" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q32" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="R32" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="S32" s="4"/>
-      <c r="T32" s="1" t="s">
+      <c r="N32" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="O32" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q32" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="R32" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="S32" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="T32" s="3"/>
+      <c r="U32" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A33" s="1">
+      <c r="V32" s="8"/>
+      <c r="W32" s="2"/>
+      <c r="X32" s="2"/>
+    </row>
+    <row r="33" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="2">
         <v>13</v>
       </c>
-      <c r="B33" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>33</v>
+      <c r="B33" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="D33" s="2">
         <v>3</v>
@@ -2139,37 +2331,43 @@
         <v>11</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="I33" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="K33" s="7"/>
-      <c r="L33" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="N33" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J33" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L33" s="2"/>
+      <c r="M33" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="N33" s="8"/>
+      <c r="O33" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="Q33" s="2">
+      <c r="R33" s="2">
         <v>0</v>
       </c>
-      <c r="T33" s="1" t="s">
+      <c r="U33" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="U33" s="8" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A34" s="1">
+      <c r="V33" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="W33" s="2"/>
+      <c r="X33" s="2"/>
+    </row>
+    <row r="34" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="2">
         <v>14</v>
       </c>
-      <c r="B34" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>33</v>
+      <c r="B34" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="D34" s="2">
         <v>4</v>
@@ -2177,36 +2375,43 @@
       <c r="E34" s="2">
         <v>12</v>
       </c>
-      <c r="I34" s="2"/>
-      <c r="K34" s="7"/>
-      <c r="L34" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="N34" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="O34" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="Q34" s="2">
+      <c r="F34" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="J34" s="2"/>
+      <c r="L34" s="2"/>
+      <c r="M34" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="N34" s="8"/>
+      <c r="O34" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="P34" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="R34" s="2">
         <v>0</v>
       </c>
-      <c r="R34" s="2">
-        <v>1</v>
-      </c>
-      <c r="T34" s="1" t="s">
+      <c r="S34" s="2">
+        <v>1</v>
+      </c>
+      <c r="U34" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A35" s="1">
+      <c r="V34" s="8"/>
+      <c r="W34" s="2"/>
+      <c r="X34" s="2"/>
+    </row>
+    <row r="35" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="2">
         <v>15</v>
       </c>
-      <c r="B35" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>33</v>
+      <c r="B35" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="D35" s="2">
         <v>4</v>
@@ -2214,38 +2419,43 @@
       <c r="E35" s="2">
         <v>13</v>
       </c>
-      <c r="G35" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="H35" s="6"/>
-      <c r="I35" s="6"/>
-      <c r="J35" s="6"/>
-      <c r="K35" s="7"/>
-      <c r="L35" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="N35" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q35" s="2">
-        <v>1</v>
-      </c>
-      <c r="R35" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="T35" s="1" t="s">
+      <c r="F35" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J35" s="2"/>
+      <c r="L35" s="2"/>
+      <c r="M35" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="N35" s="8"/>
+      <c r="O35" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="R35" s="2">
+        <v>1</v>
+      </c>
+      <c r="S35" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="U35" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A36" s="1">
+      <c r="V35" s="8"/>
+      <c r="W35" s="2"/>
+      <c r="X35" s="2"/>
+    </row>
+    <row r="36" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="2">
         <v>16</v>
       </c>
-      <c r="B36" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>33</v>
+      <c r="B36" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="D36" s="2">
         <v>4</v>
@@ -2253,44 +2463,50 @@
       <c r="E36" s="2">
         <v>14</v>
       </c>
-      <c r="I36" s="2"/>
-      <c r="J36" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="K36" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="L36" s="8" t="s">
+      <c r="F36" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="J36" s="2"/>
+      <c r="K36" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L36" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="M36" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="M36" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="N36" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="P36" s="2">
+      <c r="N36" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="O36" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q36" s="2">
         <v>4</v>
       </c>
-      <c r="Q36" s="2">
+      <c r="R36" s="2">
         <v>2</v>
       </c>
-      <c r="R36" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="T36" s="1" t="s">
+      <c r="S36" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="U36" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A37" s="1">
+      <c r="V36" s="8"/>
+      <c r="W36" s="2"/>
+      <c r="X36" s="2"/>
+    </row>
+    <row r="37" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="2">
         <v>17</v>
       </c>
-      <c r="B37" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>33</v>
+      <c r="B37" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="D37" s="2">
         <v>5</v>
@@ -2298,43 +2514,47 @@
       <c r="E37" s="2">
         <v>13</v>
       </c>
-      <c r="G37" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="H37" s="6"/>
-      <c r="I37" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J37" s="6"/>
-      <c r="K37" s="7"/>
-      <c r="L37" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="N37" s="1" t="s">
+      <c r="F37" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="J37" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L37" s="2"/>
+      <c r="M37" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="N37" s="8"/>
+      <c r="O37" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="Q37" s="6">
-        <v>1</v>
-      </c>
-      <c r="R37" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="T37" s="1" t="s">
+      <c r="R37" s="8">
+        <v>1</v>
+      </c>
+      <c r="S37" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="U37" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="U37" s="8" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A38" s="1">
+      <c r="V37" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="W37" s="2"/>
+      <c r="X37" s="2"/>
+    </row>
+    <row r="38" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A38" s="2">
         <v>18</v>
       </c>
-      <c r="B38" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>33</v>
+      <c r="B38" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="D38" s="2">
         <v>5</v>
@@ -2342,39 +2562,39 @@
       <c r="E38" s="2">
         <v>13</v>
       </c>
-      <c r="F38" s="1"/>
-      <c r="G38" s="1"/>
-      <c r="H38" s="1"/>
-      <c r="J38" s="1"/>
-      <c r="K38" s="7"/>
-      <c r="L38" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="N38" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q38" s="2">
+      <c r="J38" s="2"/>
+      <c r="L38" s="2"/>
+      <c r="M38" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="N38" s="8"/>
+      <c r="O38" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="R38" s="2">
         <v>0</v>
       </c>
-      <c r="R38" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="T38" s="1" t="s">
+      <c r="S38" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="U38" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="U38" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A39" s="1">
+      <c r="V38" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="W38" s="2"/>
+      <c r="X38" s="2"/>
+    </row>
+    <row r="39" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A39" s="2">
         <v>19</v>
       </c>
-      <c r="B39" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>33</v>
+      <c r="B39" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="D39" s="2">
         <v>5</v>
@@ -2382,38 +2602,638 @@
       <c r="E39" s="2">
         <v>15</v>
       </c>
-      <c r="F39" s="1"/>
-      <c r="G39" s="1"/>
-      <c r="H39" s="1"/>
-      <c r="K39" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="L39" s="10" t="s">
+      <c r="J39" s="2"/>
+      <c r="L39" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="M39" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="N39" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="P39" s="4">
+      <c r="N39" s="2"/>
+      <c r="O39" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q39" s="3">
         <v>3</v>
       </c>
-      <c r="Q39" s="2">
+      <c r="R39" s="2">
         <v>0</v>
       </c>
-      <c r="R39" s="2">
-        <v>1</v>
-      </c>
-      <c r="T39" s="1" t="s">
+      <c r="S39" s="2">
+        <v>1</v>
+      </c>
+      <c r="U39" s="2" t="s">
         <v>10</v>
       </c>
+      <c r="V39" s="8"/>
+      <c r="W39" s="2"/>
+      <c r="X39" s="2"/>
+    </row>
+    <row r="40" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="D40" s="1"/>
+      <c r="E40" s="1"/>
+      <c r="F40" s="1"/>
+      <c r="G40" s="1"/>
+      <c r="H40" s="1"/>
+      <c r="I40" s="1"/>
+      <c r="K40" s="1"/>
+      <c r="L40" s="1"/>
+      <c r="V40" s="7"/>
+    </row>
+    <row r="41" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="D41" s="1"/>
+      <c r="E41" s="1"/>
+      <c r="F41" s="1"/>
+      <c r="G41" s="1"/>
+      <c r="H41" s="1"/>
+      <c r="I41" s="1"/>
+      <c r="K41" s="1"/>
+      <c r="L41" s="1"/>
+      <c r="V41" s="7"/>
+    </row>
+    <row r="42" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="D42" s="1"/>
+      <c r="E42" s="1"/>
+      <c r="F42" s="1"/>
+      <c r="G42" s="1"/>
+      <c r="H42" s="1"/>
+      <c r="I42" s="1"/>
+      <c r="K42" s="1"/>
+      <c r="L42" s="1"/>
+      <c r="V42" s="7"/>
+    </row>
+    <row r="43" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="D43" s="1"/>
+      <c r="E43" s="1"/>
+      <c r="F43" s="1"/>
+      <c r="G43" s="1"/>
+      <c r="H43" s="1"/>
+      <c r="I43" s="1"/>
+      <c r="K43" s="1"/>
+      <c r="L43" s="1"/>
+      <c r="V43" s="7"/>
+    </row>
+    <row r="44" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="D44" s="1"/>
+      <c r="E44" s="1"/>
+      <c r="F44" s="1"/>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1"/>
+      <c r="I44" s="1"/>
+      <c r="K44" s="1"/>
+      <c r="L44" s="1"/>
+    </row>
+    <row r="45" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="D45" s="1"/>
+      <c r="E45" s="1"/>
+      <c r="F45" s="1"/>
+      <c r="G45" s="1"/>
+      <c r="H45" s="1"/>
+      <c r="I45" s="1"/>
+      <c r="K45" s="1"/>
+      <c r="L45" s="1"/>
+    </row>
+    <row r="46" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="D46" s="1"/>
+      <c r="E46" s="1"/>
+      <c r="F46" s="1"/>
+      <c r="G46" s="1"/>
+      <c r="H46" s="1"/>
+      <c r="I46" s="1"/>
+      <c r="K46" s="1"/>
+      <c r="L46" s="1"/>
+    </row>
+    <row r="47" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="D47" s="1"/>
+      <c r="E47" s="1"/>
+      <c r="F47" s="1"/>
+      <c r="G47" s="1"/>
+      <c r="H47" s="1"/>
+      <c r="I47" s="1"/>
+      <c r="K47" s="1"/>
+      <c r="L47" s="1"/>
+    </row>
+    <row r="48" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="D48" s="1"/>
+      <c r="E48" s="1"/>
+      <c r="F48" s="1"/>
+      <c r="G48" s="1"/>
+      <c r="H48" s="1"/>
+      <c r="I48" s="1"/>
+      <c r="K48" s="1"/>
+      <c r="L48" s="1"/>
+    </row>
+    <row r="49" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="D49" s="1"/>
+      <c r="E49" s="1"/>
+      <c r="F49" s="1"/>
+      <c r="G49" s="1"/>
+      <c r="H49" s="1"/>
+      <c r="I49" s="1"/>
+      <c r="K49" s="1"/>
+      <c r="L49" s="1"/>
+    </row>
+    <row r="50" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="D50" s="1"/>
+      <c r="E50" s="1"/>
+      <c r="F50" s="1"/>
+      <c r="G50" s="1"/>
+      <c r="H50" s="1"/>
+      <c r="I50" s="1"/>
+      <c r="K50" s="1"/>
+      <c r="L50" s="1"/>
+    </row>
+    <row r="51" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="D51" s="1"/>
+      <c r="E51" s="1"/>
+      <c r="F51" s="1"/>
+      <c r="G51" s="1"/>
+      <c r="H51" s="1"/>
+      <c r="I51" s="1"/>
+      <c r="K51" s="1"/>
+      <c r="L51" s="1"/>
+    </row>
+    <row r="52" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="D52" s="1"/>
+      <c r="E52" s="1"/>
+      <c r="F52" s="1"/>
+      <c r="G52" s="1"/>
+      <c r="H52" s="1"/>
+      <c r="I52" s="1"/>
+      <c r="K52" s="1"/>
+      <c r="L52" s="1"/>
+    </row>
+    <row r="53" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="D53" s="1"/>
+      <c r="E53" s="1"/>
+      <c r="F53" s="1"/>
+      <c r="G53" s="1"/>
+      <c r="H53" s="1"/>
+      <c r="I53" s="1"/>
+      <c r="K53" s="1"/>
+      <c r="L53" s="1"/>
+    </row>
+    <row r="54" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="D54" s="1"/>
+      <c r="E54" s="1"/>
+      <c r="F54" s="1"/>
+      <c r="G54" s="1"/>
+      <c r="H54" s="1"/>
+      <c r="I54" s="1"/>
+      <c r="K54" s="1"/>
+      <c r="L54" s="1"/>
+    </row>
+    <row r="55" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="D55" s="1"/>
+      <c r="E55" s="1"/>
+      <c r="F55" s="1"/>
+      <c r="G55" s="1"/>
+      <c r="H55" s="1"/>
+      <c r="I55" s="1"/>
+      <c r="K55" s="1"/>
+      <c r="L55" s="1"/>
+    </row>
+    <row r="56" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="D56" s="1"/>
+      <c r="E56" s="1"/>
+      <c r="F56" s="1"/>
+      <c r="G56" s="1"/>
+      <c r="H56" s="1"/>
+      <c r="I56" s="1"/>
+      <c r="K56" s="1"/>
+      <c r="L56" s="1"/>
+    </row>
+    <row r="57" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="D57" s="1"/>
+      <c r="E57" s="1"/>
+      <c r="F57" s="1"/>
+      <c r="G57" s="1"/>
+      <c r="H57" s="1"/>
+      <c r="I57" s="1"/>
+      <c r="K57" s="1"/>
+      <c r="L57" s="1"/>
+    </row>
+    <row r="58" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="D58" s="1"/>
+      <c r="E58" s="1"/>
+      <c r="F58" s="1"/>
+      <c r="G58" s="1"/>
+      <c r="H58" s="1"/>
+      <c r="I58" s="1"/>
+      <c r="K58" s="1"/>
+      <c r="L58" s="1"/>
+    </row>
+    <row r="59" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="D59" s="1"/>
+      <c r="E59" s="1"/>
+      <c r="F59" s="1"/>
+      <c r="G59" s="1"/>
+      <c r="H59" s="1"/>
+      <c r="I59" s="1"/>
+      <c r="K59" s="1"/>
+      <c r="L59" s="1"/>
+    </row>
+    <row r="60" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="D60" s="1"/>
+      <c r="E60" s="1"/>
+      <c r="F60" s="1"/>
+      <c r="G60" s="1"/>
+      <c r="H60" s="1"/>
+      <c r="I60" s="1"/>
+      <c r="K60" s="1"/>
+      <c r="L60" s="1"/>
+    </row>
+    <row r="61" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="D61" s="1"/>
+      <c r="E61" s="1"/>
+      <c r="F61" s="1"/>
+      <c r="G61" s="1"/>
+      <c r="H61" s="1"/>
+      <c r="I61" s="1"/>
+      <c r="K61" s="1"/>
+      <c r="L61" s="1"/>
+    </row>
+    <row r="62" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+      <c r="K62" s="1"/>
+      <c r="L62" s="1"/>
+    </row>
+    <row r="63" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="D63" s="1"/>
+      <c r="E63" s="1"/>
+      <c r="F63" s="1"/>
+      <c r="G63" s="1"/>
+      <c r="H63" s="1"/>
+      <c r="I63" s="1"/>
+      <c r="K63" s="1"/>
+      <c r="L63" s="1"/>
+    </row>
+    <row r="64" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="D64" s="1"/>
+      <c r="E64" s="1"/>
+      <c r="F64" s="1"/>
+      <c r="G64" s="1"/>
+      <c r="H64" s="1"/>
+      <c r="I64" s="1"/>
+      <c r="K64" s="1"/>
+      <c r="L64" s="1"/>
+    </row>
+    <row r="65" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="D65" s="1"/>
+      <c r="E65" s="1"/>
+      <c r="F65" s="1"/>
+      <c r="G65" s="1"/>
+      <c r="H65" s="1"/>
+      <c r="I65" s="1"/>
+      <c r="K65" s="1"/>
+      <c r="L65" s="1"/>
+    </row>
+    <row r="66" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="D66" s="1"/>
+      <c r="E66" s="1"/>
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="K66" s="1"/>
+      <c r="L66" s="1"/>
+    </row>
+    <row r="67" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="D67" s="1"/>
+      <c r="E67" s="1"/>
+      <c r="F67" s="1"/>
+      <c r="G67" s="1"/>
+      <c r="H67" s="1"/>
+      <c r="I67" s="1"/>
+      <c r="K67" s="1"/>
+      <c r="L67" s="1"/>
+    </row>
+    <row r="68" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="D68" s="1"/>
+      <c r="E68" s="1"/>
+      <c r="F68" s="1"/>
+      <c r="G68" s="1"/>
+      <c r="H68" s="1"/>
+      <c r="I68" s="1"/>
+      <c r="K68" s="1"/>
+      <c r="L68" s="1"/>
+    </row>
+    <row r="69" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="D69" s="1"/>
+      <c r="E69" s="1"/>
+      <c r="F69" s="1"/>
+      <c r="G69" s="1"/>
+      <c r="H69" s="1"/>
+      <c r="I69" s="1"/>
+      <c r="K69" s="1"/>
+      <c r="L69" s="1"/>
+    </row>
+    <row r="70" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="D70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="K70" s="1"/>
+      <c r="L70" s="1"/>
+    </row>
+    <row r="71" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="D71" s="1"/>
+      <c r="E71" s="1"/>
+      <c r="F71" s="1"/>
+      <c r="G71" s="1"/>
+      <c r="H71" s="1"/>
+      <c r="I71" s="1"/>
+      <c r="K71" s="1"/>
+      <c r="L71" s="1"/>
+    </row>
+    <row r="72" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="D72" s="1"/>
+      <c r="E72" s="1"/>
+      <c r="F72" s="1"/>
+      <c r="G72" s="1"/>
+      <c r="H72" s="1"/>
+      <c r="I72" s="1"/>
+      <c r="K72" s="1"/>
+      <c r="L72" s="1"/>
+    </row>
+    <row r="73" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="D73" s="1"/>
+      <c r="E73" s="1"/>
+      <c r="F73" s="1"/>
+      <c r="G73" s="1"/>
+      <c r="H73" s="1"/>
+      <c r="I73" s="1"/>
+      <c r="K73" s="1"/>
+      <c r="L73" s="1"/>
+    </row>
+    <row r="74" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="D74" s="1"/>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1"/>
+      <c r="K74" s="1"/>
+      <c r="L74" s="1"/>
+    </row>
+    <row r="75" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="D75" s="1"/>
+      <c r="E75" s="1"/>
+      <c r="F75" s="1"/>
+      <c r="G75" s="1"/>
+      <c r="H75" s="1"/>
+      <c r="I75" s="1"/>
+      <c r="K75" s="1"/>
+      <c r="L75" s="1"/>
+    </row>
+    <row r="76" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="D76" s="1"/>
+      <c r="E76" s="1"/>
+      <c r="F76" s="1"/>
+      <c r="G76" s="1"/>
+      <c r="H76" s="1"/>
+      <c r="I76" s="1"/>
+      <c r="K76" s="1"/>
+      <c r="L76" s="1"/>
+    </row>
+    <row r="77" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="D77" s="1"/>
+      <c r="E77" s="1"/>
+      <c r="F77" s="1"/>
+      <c r="G77" s="1"/>
+      <c r="H77" s="1"/>
+      <c r="I77" s="1"/>
+      <c r="K77" s="1"/>
+      <c r="L77" s="1"/>
+    </row>
+    <row r="78" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="D78" s="1"/>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+      <c r="K78" s="1"/>
+      <c r="L78" s="1"/>
+    </row>
+    <row r="79" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="D79" s="1"/>
+      <c r="E79" s="1"/>
+      <c r="F79" s="1"/>
+      <c r="G79" s="1"/>
+      <c r="H79" s="1"/>
+      <c r="I79" s="1"/>
+      <c r="K79" s="1"/>
+      <c r="L79" s="1"/>
+    </row>
+    <row r="80" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="D80" s="1"/>
+      <c r="E80" s="1"/>
+      <c r="F80" s="1"/>
+      <c r="G80" s="1"/>
+      <c r="H80" s="1"/>
+      <c r="I80" s="1"/>
+      <c r="K80" s="1"/>
+      <c r="L80" s="1"/>
+    </row>
+    <row r="81" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="D81" s="1"/>
+      <c r="E81" s="1"/>
+      <c r="F81" s="1"/>
+      <c r="G81" s="1"/>
+      <c r="H81" s="1"/>
+      <c r="I81" s="1"/>
+      <c r="K81" s="1"/>
+      <c r="L81" s="1"/>
+    </row>
+    <row r="82" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="D82" s="1"/>
+      <c r="E82" s="1"/>
+      <c r="F82" s="1"/>
+      <c r="G82" s="1"/>
+      <c r="H82" s="1"/>
+      <c r="I82" s="1"/>
+      <c r="K82" s="1"/>
+      <c r="L82" s="1"/>
+    </row>
+    <row r="83" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="D83" s="1"/>
+      <c r="E83" s="1"/>
+      <c r="F83" s="1"/>
+      <c r="G83" s="1"/>
+      <c r="H83" s="1"/>
+      <c r="I83" s="1"/>
+      <c r="K83" s="1"/>
+      <c r="L83" s="1"/>
+    </row>
+    <row r="84" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="D84" s="1"/>
+      <c r="E84" s="1"/>
+      <c r="F84" s="1"/>
+      <c r="G84" s="1"/>
+      <c r="H84" s="1"/>
+      <c r="I84" s="1"/>
+      <c r="K84" s="1"/>
+      <c r="L84" s="1"/>
+    </row>
+    <row r="85" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="D85" s="1"/>
+      <c r="E85" s="1"/>
+      <c r="F85" s="1"/>
+      <c r="G85" s="1"/>
+      <c r="H85" s="1"/>
+      <c r="I85" s="1"/>
+      <c r="K85" s="1"/>
+      <c r="L85" s="1"/>
+    </row>
+    <row r="86" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="D86" s="1"/>
+      <c r="E86" s="1"/>
+      <c r="F86" s="1"/>
+      <c r="G86" s="1"/>
+      <c r="H86" s="1"/>
+      <c r="I86" s="1"/>
+      <c r="K86" s="1"/>
+      <c r="L86" s="1"/>
+    </row>
+    <row r="87" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="D87" s="1"/>
+      <c r="E87" s="1"/>
+      <c r="F87" s="1"/>
+      <c r="G87" s="1"/>
+      <c r="H87" s="1"/>
+      <c r="I87" s="1"/>
+      <c r="K87" s="1"/>
+      <c r="L87" s="1"/>
+    </row>
+    <row r="88" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="D88" s="1"/>
+      <c r="E88" s="1"/>
+      <c r="F88" s="1"/>
+      <c r="G88" s="1"/>
+      <c r="H88" s="1"/>
+      <c r="I88" s="1"/>
+      <c r="K88" s="1"/>
+      <c r="L88" s="1"/>
+    </row>
+    <row r="89" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="D89" s="1"/>
+      <c r="E89" s="1"/>
+      <c r="F89" s="1"/>
+      <c r="G89" s="1"/>
+      <c r="H89" s="1"/>
+      <c r="I89" s="1"/>
+      <c r="K89" s="1"/>
+      <c r="L89" s="1"/>
+    </row>
+    <row r="90" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="D90" s="1"/>
+      <c r="E90" s="1"/>
+      <c r="F90" s="1"/>
+      <c r="G90" s="1"/>
+      <c r="H90" s="1"/>
+      <c r="I90" s="1"/>
+      <c r="K90" s="1"/>
+      <c r="L90" s="1"/>
+    </row>
+    <row r="91" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="D91" s="1"/>
+      <c r="E91" s="1"/>
+      <c r="F91" s="1"/>
+      <c r="G91" s="1"/>
+      <c r="H91" s="1"/>
+      <c r="I91" s="1"/>
+      <c r="K91" s="1"/>
+      <c r="L91" s="1"/>
+    </row>
+    <row r="92" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="D92" s="1"/>
+      <c r="E92" s="1"/>
+      <c r="F92" s="1"/>
+      <c r="G92" s="1"/>
+      <c r="H92" s="1"/>
+      <c r="I92" s="1"/>
+      <c r="K92" s="1"/>
+      <c r="L92" s="1"/>
+    </row>
+    <row r="93" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="D93" s="1"/>
+      <c r="E93" s="1"/>
+      <c r="F93" s="1"/>
+      <c r="G93" s="1"/>
+      <c r="H93" s="1"/>
+      <c r="I93" s="1"/>
+      <c r="K93" s="1"/>
+      <c r="L93" s="1"/>
+    </row>
+    <row r="94" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="D94" s="1"/>
+      <c r="E94" s="1"/>
+      <c r="F94" s="1"/>
+      <c r="G94" s="1"/>
+      <c r="H94" s="1"/>
+      <c r="I94" s="1"/>
+      <c r="K94" s="1"/>
+      <c r="L94" s="1"/>
+    </row>
+    <row r="95" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="D95" s="1"/>
+      <c r="E95" s="1"/>
+      <c r="F95" s="1"/>
+      <c r="G95" s="1"/>
+      <c r="H95" s="1"/>
+      <c r="I95" s="1"/>
+      <c r="K95" s="1"/>
+      <c r="L95" s="1"/>
+    </row>
+    <row r="96" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="D96" s="1"/>
+      <c r="E96" s="1"/>
+      <c r="F96" s="1"/>
+      <c r="G96" s="1"/>
+      <c r="H96" s="1"/>
+      <c r="I96" s="1"/>
+      <c r="K96" s="1"/>
+      <c r="L96" s="1"/>
+    </row>
+    <row r="97" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="D97" s="1"/>
+      <c r="E97" s="1"/>
+      <c r="F97" s="1"/>
+      <c r="G97" s="1"/>
+      <c r="H97" s="1"/>
+      <c r="I97" s="1"/>
+      <c r="K97" s="1"/>
+      <c r="L97" s="1"/>
+    </row>
+    <row r="98" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="D98" s="1"/>
+      <c r="E98" s="1"/>
+      <c r="F98" s="1"/>
+      <c r="G98" s="1"/>
+      <c r="H98" s="1"/>
+      <c r="I98" s="1"/>
+      <c r="K98" s="1"/>
+      <c r="L98" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="B1:U39" xr:uid="{E5603586-01B1-45C3-888E-EC2BF5D85650}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B21:U39">
+  <autoFilter ref="A1:V98" xr:uid="{E5603586-01B1-45C3-888E-EC2BF5D85650}">
+    <filterColumn colId="5">
+      <filters blank="1"/>
+    </filterColumn>
+  </autoFilter>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B21:V39">
     <sortCondition ref="D21:D39"/>
     <sortCondition ref="E21:E39"/>
   </sortState>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/Dane/karty_v1.xlsx
+++ b/Dane/karty_v1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a40667ca9a5261e0/Dokumenty/Dokumenty/Gra Walka o Dusze/Symulator/Dane/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="89" documentId="8_{C60639C0-3DC1-46DF-8FF5-DD98044E12E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FDF2BB4B-088A-4B8C-A50A-91B0457261CB}"/>
+  <xr:revisionPtr revIDLastSave="116" documentId="8_{C60639C0-3DC1-46DF-8FF5-DD98044E12E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{80763C81-E1F9-420E-B8B9-DDA2F3FD6DC3}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1C612D17-AB6F-4FCE-AA6C-1D2201D34FB7}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Arkusz1!$A$1:$V$98</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Arkusz1!$A$1:$X$40</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,8 +27,70 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Mariusz Janeczko</author>
+  </authors>
+  <commentList>
+    <comment ref="H15" authorId="0" shapeId="0" xr:uid="{99EB7673-5FD0-4BC1-9BA0-E90A43A21D65}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="238"/>
+          </rPr>
+          <t>Mariusz Janeczko:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="238"/>
+          </rPr>
+          <t xml:space="preserve">
+ZYCIE - zdolnosc nr 1 to ocalenie przeciwnika, dolnosc nr 2 to zabicie śmierci</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H34" authorId="0" shapeId="0" xr:uid="{A6E5B52D-9858-4032-ADC8-5AB9224B7549}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="238"/>
+          </rPr>
+          <t>Mariusz Janeczko:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="238"/>
+          </rPr>
+          <t xml:space="preserve">
+specjalna ile razy uniknie smierci</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="98">
   <si>
     <t>klasa</t>
   </si>
@@ -307,13 +369,28 @@
   </si>
   <si>
     <t>klasa_wroga&lt;</t>
+  </si>
+  <si>
+    <t>liczba_zdolnosci_walk</t>
+  </si>
+  <si>
+    <t>6,3</t>
+  </si>
+  <si>
+    <t>testowana</t>
+  </si>
+  <si>
+    <t>t</t>
+  </si>
+  <si>
+    <t>b</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
@@ -359,6 +436,21 @@
       <family val="2"/>
       <charset val="238"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <charset val="238"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <charset val="238"/>
     </font>
   </fonts>
   <fills count="3">
@@ -735,36 +827,37 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5603586-01B1-45C3-888E-EC2BF5D85650}">
-  <sheetPr codeName="Arkusz1" filterMode="1"/>
-  <dimension ref="A1:X98"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5603586-01B1-45C3-888E-EC2BF5D85650}">
+  <sheetPr codeName="Arkusz1"/>
+  <dimension ref="A1:Z98"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="15.85546875" style="1" customWidth="1"/>
     <col min="3" max="3" width="9.140625" style="1"/>
     <col min="4" max="5" width="9.140625" style="2"/>
-    <col min="6" max="6" width="19.28515625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="24.85546875" style="2" customWidth="1"/>
-    <col min="8" max="8" width="27.7109375" style="2" customWidth="1"/>
-    <col min="9" max="9" width="26" style="2" customWidth="1"/>
-    <col min="10" max="10" width="15.5703125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="19.7109375" style="2" customWidth="1"/>
-    <col min="12" max="12" width="19.42578125" style="5" customWidth="1"/>
-    <col min="13" max="13" width="23.5703125" style="1" customWidth="1"/>
-    <col min="14" max="14" width="19" style="1" customWidth="1"/>
-    <col min="15" max="15" width="9.140625" style="1"/>
-    <col min="16" max="16" width="11" style="2" customWidth="1"/>
-    <col min="17" max="17" width="10.7109375" style="2" customWidth="1"/>
-    <col min="18" max="18" width="10.140625" style="2" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="2" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="2" customWidth="1"/>
-    <col min="21" max="21" width="12.5703125" style="1" customWidth="1"/>
-    <col min="22" max="22" width="18" style="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="6" max="7" width="19.28515625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="20.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="24.85546875" style="2" customWidth="1"/>
+    <col min="10" max="10" width="27.7109375" style="2" customWidth="1"/>
+    <col min="11" max="11" width="26" style="2" customWidth="1"/>
+    <col min="12" max="12" width="15.5703125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="19.7109375" style="2" customWidth="1"/>
+    <col min="14" max="14" width="19.42578125" style="5" customWidth="1"/>
+    <col min="15" max="15" width="23.5703125" style="1" customWidth="1"/>
+    <col min="16" max="16" width="19" style="1" customWidth="1"/>
+    <col min="17" max="17" width="9.140625" style="1"/>
+    <col min="18" max="18" width="11" style="2" customWidth="1"/>
+    <col min="19" max="19" width="10.7109375" style="2" customWidth="1"/>
+    <col min="20" max="20" width="10.140625" style="2" customWidth="1"/>
+    <col min="21" max="21" width="14.7109375" style="2" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="2" customWidth="1"/>
+    <col min="23" max="23" width="12.5703125" style="1" customWidth="1"/>
+    <col min="24" max="24" width="18" style="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>53</v>
       </c>
@@ -784,55 +877,61 @@
         <v>88</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="R1" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="S1" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="T1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="U1" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="V1" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -851,209 +950,261 @@
       <c r="F2" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="J2" s="2"/>
-      <c r="L2" s="2" t="s">
+      <c r="H2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L2" s="2"/>
+      <c r="N2" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="M2" s="8" t="s">
+      <c r="O2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="8"/>
-      <c r="O2" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="R2" s="2">
+      <c r="P2" s="8"/>
+      <c r="Q2" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="T2" s="2">
         <v>0</v>
       </c>
-      <c r="U2" s="2" t="s">
+      <c r="W2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="V2" s="2" t="s">
+      <c r="X2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="W2" s="2"/>
-      <c r="X2" s="2"/>
-    </row>
-    <row r="3" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
+      <c r="Y2" s="2"/>
+      <c r="Z2" s="2"/>
+    </row>
+    <row r="3" spans="1:26" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="8">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="2">
-        <v>1</v>
-      </c>
-      <c r="E3" s="2">
+      <c r="D3" s="8">
+        <v>1</v>
+      </c>
+      <c r="E3" s="8">
         <v>2</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="J3" s="2"/>
-      <c r="L3" s="2" t="s">
+      <c r="G3" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="8"/>
+      <c r="L3" s="8"/>
+      <c r="M3" s="8"/>
+      <c r="N3" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="M3" s="8" t="s">
+      <c r="O3" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="N3" s="8"/>
-      <c r="O3" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="R3" s="2">
+      <c r="P3" s="8"/>
+      <c r="Q3" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="R3" s="8"/>
+      <c r="S3" s="8"/>
+      <c r="T3" s="8">
         <v>0</v>
       </c>
-      <c r="T3" s="2">
+      <c r="U3" s="8"/>
+      <c r="V3" s="8">
         <v>-1</v>
       </c>
-      <c r="U3" s="2" t="s">
+      <c r="W3" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="V3" s="2" t="s">
+      <c r="X3" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="W3" s="2"/>
-      <c r="X3" s="2"/>
-    </row>
-    <row r="4" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
+      <c r="Y3" s="8"/>
+      <c r="Z3" s="8"/>
+    </row>
+    <row r="4" spans="1:26" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="8">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="2">
-        <v>1</v>
-      </c>
-      <c r="E4" s="2">
+      <c r="D4" s="8">
+        <v>1</v>
+      </c>
+      <c r="E4" s="8">
         <v>3</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="G4" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="J4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="8" t="s">
-        <v>8</v>
-      </c>
+      <c r="K4" s="8"/>
+      <c r="L4" s="8"/>
+      <c r="M4" s="8"/>
       <c r="N4" s="8"/>
       <c r="O4" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="P4" s="2" t="s">
+      <c r="P4" s="8"/>
+      <c r="Q4" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="R4" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="R4" s="2">
+      <c r="S4" s="8"/>
+      <c r="T4" s="8">
         <v>0</v>
       </c>
-      <c r="S4" s="2">
+      <c r="U4" s="8">
         <v>2</v>
       </c>
-      <c r="U4" s="2" t="s">
+      <c r="V4" s="8"/>
+      <c r="W4" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="V4" s="2"/>
-      <c r="W4" s="2"/>
-      <c r="X4" s="2"/>
-    </row>
-    <row r="5" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2">
+      <c r="X4" s="8"/>
+      <c r="Y4" s="8"/>
+      <c r="Z4" s="8"/>
+    </row>
+    <row r="5" spans="1:26" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="8">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="2">
-        <v>1</v>
-      </c>
-      <c r="E5" s="2">
+      <c r="D5" s="8">
+        <v>1</v>
+      </c>
+      <c r="E5" s="8">
         <v>4</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="I5" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="J5" s="2"/>
-      <c r="L5" s="2"/>
-      <c r="M5" s="8" t="s">
-        <v>8</v>
-      </c>
+      <c r="J5" s="8"/>
+      <c r="K5" s="8"/>
+      <c r="L5" s="8"/>
+      <c r="M5" s="8"/>
       <c r="N5" s="8"/>
       <c r="O5" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="R5" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="S5" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="U5" s="2" t="s">
+      <c r="P5" s="8"/>
+      <c r="Q5" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="R5" s="8"/>
+      <c r="S5" s="8"/>
+      <c r="T5" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="U5" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="V5" s="8"/>
+      <c r="W5" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="V5" s="2"/>
-      <c r="W5" s="2"/>
-      <c r="X5" s="2"/>
-    </row>
-    <row r="6" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
+      <c r="X5" s="8"/>
+      <c r="Y5" s="8"/>
+      <c r="Z5" s="8"/>
+    </row>
+    <row r="6" spans="1:26" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="8">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="2">
-        <v>1</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="D6" s="8">
+        <v>1</v>
+      </c>
+      <c r="E6" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="J6" s="2"/>
-      <c r="L6" s="2"/>
-      <c r="M6" s="8" t="s">
-        <v>8</v>
-      </c>
+      <c r="G6" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
+      <c r="K6" s="8"/>
+      <c r="L6" s="8"/>
+      <c r="M6" s="8"/>
       <c r="N6" s="8"/>
       <c r="O6" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="R6" s="2">
+      <c r="P6" s="8"/>
+      <c r="Q6" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="R6" s="8"/>
+      <c r="S6" s="8"/>
+      <c r="T6" s="8">
         <v>0</v>
       </c>
-      <c r="S6" s="2">
-        <v>1</v>
-      </c>
-      <c r="U6" s="2" t="s">
+      <c r="U6" s="8">
+        <v>1</v>
+      </c>
+      <c r="V6" s="8"/>
+      <c r="W6" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="V6" s="2" t="s">
+      <c r="X6" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="W6" s="2"/>
-      <c r="X6" s="2"/>
-    </row>
-    <row r="7" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+      <c r="Y6" s="8"/>
+      <c r="Z6" s="8"/>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -1072,38 +1223,41 @@
       <c r="F7" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="L7" s="2" t="s">
+      <c r="H7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N7" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="M7" s="8" t="s">
+      <c r="O7" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="N7" s="8" t="s">
+      <c r="P7" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="O7" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="R7" s="2" t="s">
+      <c r="Q7" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="T7" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="S7" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="U7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="W7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="V7" s="2" t="s">
+      <c r="X7" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="W7" s="2"/>
-      <c r="X7" s="2"/>
-    </row>
-    <row r="8" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+      <c r="Y7" s="2"/>
+      <c r="Z7" s="2"/>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -1122,36 +1276,39 @@
       <c r="F8" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2" t="s">
+      <c r="H8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="L8" s="2" t="s">
+      <c r="N8" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M8" s="8" t="s">
+      <c r="O8" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="N8" s="8" t="s">
+      <c r="P8" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="O8" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="R8" s="2">
+      <c r="Q8" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="T8" s="2">
         <v>0</v>
       </c>
-      <c r="S8" s="2">
-        <v>1</v>
-      </c>
-      <c r="U8" s="2" t="s">
+      <c r="U8" s="2">
+        <v>1</v>
+      </c>
+      <c r="W8" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="V8" s="2"/>
-      <c r="W8" s="2"/>
       <c r="X8" s="2"/>
-    </row>
-    <row r="9" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+      <c r="Y8" s="2"/>
+      <c r="Z8" s="2"/>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -1170,41 +1327,44 @@
       <c r="F9" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2" t="s">
+      <c r="H9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="L9" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="M9" s="8" t="s">
+      <c r="N9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O9" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="N9" s="8" t="s">
+      <c r="P9" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="O9" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="P9" s="2">
+      <c r="Q9" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="R9" s="2">
         <v>-1</v>
       </c>
-      <c r="R9" s="2">
+      <c r="T9" s="2">
         <v>0</v>
       </c>
-      <c r="S9" s="2">
-        <v>1</v>
-      </c>
-      <c r="U9" s="2" t="s">
+      <c r="U9" s="2">
+        <v>1</v>
+      </c>
+      <c r="W9" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="V9" s="2" t="s">
+      <c r="X9" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="W9" s="2"/>
-      <c r="X9" s="2"/>
-    </row>
-    <row r="10" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+      <c r="Y9" s="2"/>
+      <c r="Z9" s="2"/>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -1223,43 +1383,46 @@
       <c r="F10" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="J10" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K10" s="2" t="s">
+      <c r="H10" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M10" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="L10" s="2" t="s">
+      <c r="N10" s="2" t="s">
         <v>69</v>
-      </c>
-      <c r="M10" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="N10" s="8" t="s">
-        <v>75</v>
       </c>
       <c r="O10" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="P10" s="2" t="s">
+      <c r="P10" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q10" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="R10" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="R10" s="2">
-        <v>1</v>
-      </c>
-      <c r="S10" s="2">
+      <c r="T10" s="2">
+        <v>1</v>
+      </c>
+      <c r="U10" s="2">
         <v>2</v>
       </c>
-      <c r="U10" s="2" t="s">
+      <c r="W10" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="V10" s="2" t="s">
+      <c r="X10" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="W10" s="2"/>
-      <c r="X10" s="2"/>
-    </row>
-    <row r="11" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+      <c r="Y10" s="2"/>
+      <c r="Z10" s="2"/>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -1279,36 +1442,39 @@
         <v>89</v>
       </c>
       <c r="H11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J11" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="J11" s="2"/>
       <c r="L11" s="2"/>
-      <c r="M11" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="N11" s="8"/>
+      <c r="N11" s="2"/>
       <c r="O11" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="P11" s="4" t="s">
+      <c r="P11" s="8"/>
+      <c r="Q11" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="R11" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="R11" s="2">
-        <v>1</v>
-      </c>
-      <c r="S11" s="2">
+      <c r="T11" s="2">
+        <v>1</v>
+      </c>
+      <c r="U11" s="2">
         <v>2</v>
       </c>
-      <c r="U11" s="2" t="s">
+      <c r="W11" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="V11" s="2" t="s">
+      <c r="X11" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="W11" s="2"/>
-      <c r="X11" s="2"/>
-    </row>
-    <row r="12" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+      <c r="Y11" s="2"/>
+      <c r="Z11" s="2"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -1327,41 +1493,44 @@
       <c r="F12" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="H12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="J12" s="2"/>
-      <c r="K12" s="4" t="s">
+      <c r="L12" s="2"/>
+      <c r="M12" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="L12" s="2" t="s">
+      <c r="N12" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="M12" s="8" t="s">
+      <c r="O12" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="N12" s="8" t="s">
+      <c r="P12" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="O12" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="R12" s="2">
+      <c r="Q12" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="T12" s="2">
         <v>0</v>
       </c>
-      <c r="T12" s="2">
-        <v>1</v>
-      </c>
-      <c r="U12" s="2" t="s">
+      <c r="V12" s="2">
+        <v>1</v>
+      </c>
+      <c r="W12" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="V12" s="2" t="s">
+      <c r="X12" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="W12" s="2"/>
-      <c r="X12" s="2"/>
-    </row>
-    <row r="13" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+      <c r="Y12" s="2"/>
+      <c r="Z12" s="2"/>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -1380,32 +1549,38 @@
       <c r="F13" s="2" t="s">
         <v>89</v>
       </c>
+      <c r="G13" s="2" t="s">
+        <v>96</v>
+      </c>
       <c r="H13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J13" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="J13" s="2"/>
       <c r="L13" s="2"/>
-      <c r="M13" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="N13" s="8"/>
+      <c r="N13" s="2"/>
       <c r="O13" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="R13" s="2">
+      <c r="P13" s="8"/>
+      <c r="Q13" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="T13" s="2">
         <v>0</v>
       </c>
-      <c r="S13" s="2">
-        <v>1</v>
-      </c>
-      <c r="U13" s="2" t="s">
+      <c r="U13" s="2">
+        <v>1</v>
+      </c>
+      <c r="W13" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="V13" s="2"/>
-      <c r="W13" s="2"/>
       <c r="X13" s="2"/>
-    </row>
-    <row r="14" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+      <c r="Y13" s="2"/>
+      <c r="Z13" s="2"/>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -1425,38 +1600,44 @@
         <v>91</v>
       </c>
       <c r="G14" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="I14" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="J14" s="2" t="s">
+      <c r="L14" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="L14" s="2"/>
-      <c r="M14" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="N14" s="8"/>
+      <c r="N14" s="2"/>
       <c r="O14" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="P14" s="8"/>
+      <c r="Q14" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="Q14" s="2">
+      <c r="S14" s="2">
         <v>-3</v>
       </c>
-      <c r="R14" s="2" t="s">
+      <c r="T14" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="S14" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="U14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="W14" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="V14" s="8" t="s">
+      <c r="X14" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="W14" s="2"/>
-      <c r="X14" s="2"/>
-    </row>
-    <row r="15" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+      <c r="Y14" s="2"/>
+      <c r="Z14" s="2"/>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -1475,31 +1656,34 @@
       <c r="F15" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="J15" s="2"/>
+      <c r="H15" s="2" t="s">
+        <v>23</v>
+      </c>
       <c r="L15" s="2"/>
-      <c r="M15" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="N15" s="8"/>
+      <c r="N15" s="2"/>
       <c r="O15" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="R15" s="2">
+      <c r="P15" s="8"/>
+      <c r="Q15" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="T15" s="2">
         <v>0</v>
       </c>
-      <c r="S15" s="2">
-        <v>1</v>
-      </c>
-      <c r="U15" s="2" t="s">
+      <c r="U15" s="2">
+        <v>1</v>
+      </c>
+      <c r="W15" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="V15" s="8" t="s">
+      <c r="X15" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="W15" s="2"/>
-      <c r="X15" s="2"/>
-    </row>
-    <row r="16" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+      <c r="Y15" s="2"/>
+      <c r="Z15" s="2"/>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -1518,33 +1702,39 @@
       <c r="F16" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="J16" s="2"/>
-      <c r="L16" s="2" t="s">
+      <c r="H16" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="N16" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="M16" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="N16" s="8"/>
       <c r="O16" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="R16" s="2">
+      <c r="P16" s="8"/>
+      <c r="Q16" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="T16" s="2">
         <v>0</v>
       </c>
-      <c r="T16" s="2">
+      <c r="V16" s="2">
         <v>2</v>
       </c>
-      <c r="U16" s="2" t="s">
+      <c r="W16" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="V16" s="2" t="s">
+      <c r="X16" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="W16" s="2"/>
-      <c r="X16" s="2"/>
-    </row>
-    <row r="17" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+      <c r="Y16" s="2"/>
+      <c r="Z16" s="2"/>
+    </row>
+    <row r="17" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -1563,40 +1753,43 @@
       <c r="F17" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="G17" s="2" t="s">
+      <c r="H17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="H17" s="2" t="s">
+      <c r="J17" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="I17" s="2" t="s">
+      <c r="K17" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="J17" s="2"/>
       <c r="L17" s="2"/>
-      <c r="M17" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="N17" s="8"/>
+      <c r="N17" s="2"/>
       <c r="O17" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="R17" s="2">
+      <c r="P17" s="8"/>
+      <c r="Q17" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="T17" s="2">
         <v>0</v>
       </c>
-      <c r="S17" s="2">
-        <v>1</v>
-      </c>
-      <c r="U17" s="2" t="s">
+      <c r="U17" s="2">
+        <v>1</v>
+      </c>
+      <c r="W17" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="V17" s="2" t="s">
+      <c r="X17" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="W17" s="2"/>
-      <c r="X17" s="2"/>
-    </row>
-    <row r="18" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+      <c r="Y17" s="2"/>
+      <c r="Z17" s="2"/>
+    </row>
+    <row r="18" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -1616,34 +1809,37 @@
         <v>89</v>
       </c>
       <c r="H18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J18" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="J18" s="2"/>
       <c r="L18" s="2"/>
-      <c r="M18" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="N18" s="8"/>
+      <c r="N18" s="2"/>
       <c r="O18" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="P18" s="2">
+      <c r="P18" s="8"/>
+      <c r="Q18" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="R18" s="2">
         <v>-3</v>
       </c>
-      <c r="R18" s="2">
+      <c r="T18" s="2">
         <v>0</v>
       </c>
-      <c r="S18" s="2">
-        <v>1</v>
-      </c>
-      <c r="U18" s="2" t="s">
+      <c r="U18" s="2">
+        <v>1</v>
+      </c>
+      <c r="W18" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="V18" s="2"/>
-      <c r="W18" s="2"/>
       <c r="X18" s="2"/>
-    </row>
-    <row r="19" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+      <c r="Y18" s="2"/>
+      <c r="Z18" s="2"/>
+    </row>
+    <row r="19" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -1663,30 +1859,36 @@
         <v>91</v>
       </c>
       <c r="G19" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="I19" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="J19" s="2" t="s">
+      <c r="L19" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="L19" s="2"/>
-      <c r="M19" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="N19" s="8"/>
+      <c r="N19" s="2"/>
       <c r="O19" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="P19" s="8"/>
+      <c r="Q19" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="R19" s="2">
+      <c r="T19" s="2">
         <v>0</v>
       </c>
-      <c r="U19" s="2" t="s">
+      <c r="W19" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="V19" s="2"/>
-      <c r="W19" s="2"/>
       <c r="X19" s="2"/>
-    </row>
-    <row r="20" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+      <c r="Y19" s="2"/>
+      <c r="Z19" s="2"/>
+    </row>
+    <row r="20" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -1705,29 +1907,35 @@
       <c r="F20" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="J20" s="2"/>
+      <c r="G20" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>54</v>
+      </c>
       <c r="L20" s="2"/>
-      <c r="M20" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="N20" s="8"/>
+      <c r="N20" s="2"/>
       <c r="O20" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="R20" s="2">
+      <c r="P20" s="8"/>
+      <c r="Q20" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="T20" s="2">
         <v>0</v>
       </c>
-      <c r="S20" s="2">
-        <v>1</v>
-      </c>
-      <c r="U20" s="2" t="s">
+      <c r="U20" s="2">
+        <v>1</v>
+      </c>
+      <c r="W20" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="V20" s="2"/>
-      <c r="W20" s="2"/>
       <c r="X20" s="2"/>
-    </row>
-    <row r="21" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+      <c r="Y20" s="2"/>
+      <c r="Z20" s="2"/>
+    </row>
+    <row r="21" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>1</v>
       </c>
@@ -1746,220 +1954,271 @@
       <c r="F21" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="J21" s="2"/>
-      <c r="L21" s="2" t="s">
+      <c r="H21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L21" s="2"/>
+      <c r="N21" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="M21" s="8" t="s">
+      <c r="O21" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="N21" s="8"/>
-      <c r="O21" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="R21" s="2">
+      <c r="P21" s="8"/>
+      <c r="Q21" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="T21" s="2">
         <v>0</v>
       </c>
-      <c r="U21" s="2" t="s">
+      <c r="W21" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="V21" s="2" t="s">
+      <c r="X21" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="W21" s="2"/>
-      <c r="X21" s="2"/>
-    </row>
-    <row r="22" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="2">
+      <c r="Y21" s="2"/>
+      <c r="Z21" s="2"/>
+    </row>
+    <row r="22" spans="1:26" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="8">
         <v>2</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="D22" s="2">
-        <v>1</v>
-      </c>
-      <c r="E22" s="2">
+      <c r="D22" s="8">
+        <v>1</v>
+      </c>
+      <c r="E22" s="8">
         <v>2</v>
       </c>
-      <c r="F22" s="2" t="s">
+      <c r="F22" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="G22" s="2" t="s">
+      <c r="G22" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="I22" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="I22" s="2" t="s">
+      <c r="J22" s="8"/>
+      <c r="K22" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="J22" s="2"/>
-      <c r="L22" s="2"/>
-      <c r="M22" s="8" t="s">
-        <v>8</v>
-      </c>
+      <c r="L22" s="8"/>
+      <c r="M22" s="8"/>
       <c r="N22" s="8"/>
       <c r="O22" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="P22" s="2">
-        <v>1</v>
-      </c>
-      <c r="R22" s="2">
-        <v>1</v>
-      </c>
-      <c r="S22" s="2">
-        <v>1</v>
-      </c>
-      <c r="U22" s="2" t="s">
+      <c r="P22" s="8"/>
+      <c r="Q22" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="R22" s="8">
+        <v>1</v>
+      </c>
+      <c r="S22" s="8"/>
+      <c r="T22" s="8">
+        <v>1</v>
+      </c>
+      <c r="U22" s="8">
+        <v>1</v>
+      </c>
+      <c r="V22" s="8"/>
+      <c r="W22" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="V22" s="2" t="s">
+      <c r="X22" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="W22" s="2"/>
-      <c r="X22" s="2"/>
-    </row>
-    <row r="23" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="2">
+      <c r="Y22" s="8"/>
+      <c r="Z22" s="8"/>
+    </row>
+    <row r="23" spans="1:26" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="8">
         <v>3</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="D23" s="2">
-        <v>1</v>
-      </c>
-      <c r="E23" s="2">
+      <c r="D23" s="8">
+        <v>1</v>
+      </c>
+      <c r="E23" s="8">
         <v>3</v>
       </c>
-      <c r="F23" s="2" t="s">
+      <c r="F23" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="J23" s="2"/>
-      <c r="K23" s="2">
-        <v>1</v>
-      </c>
-      <c r="L23" s="2" t="s">
+      <c r="G23" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="I23" s="8"/>
+      <c r="J23" s="8"/>
+      <c r="K23" s="8"/>
+      <c r="L23" s="8"/>
+      <c r="M23" s="8">
+        <v>1</v>
+      </c>
+      <c r="N23" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="M23" s="8" t="s">
+      <c r="O23" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="N23" s="8" t="s">
+      <c r="P23" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="O23" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="R23" s="2">
+      <c r="Q23" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="R23" s="8"/>
+      <c r="S23" s="8"/>
+      <c r="T23" s="8">
         <v>0</v>
       </c>
-      <c r="U23" s="2" t="s">
+      <c r="U23" s="8"/>
+      <c r="V23" s="8"/>
+      <c r="W23" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="V23" s="2" t="s">
+      <c r="X23" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="W23" s="2"/>
-      <c r="X23" s="2"/>
-    </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A24" s="2">
+      <c r="Y23" s="8"/>
+      <c r="Z23" s="8"/>
+    </row>
+    <row r="24" spans="1:26" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="8">
         <v>4</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="D24" s="2">
-        <v>1</v>
-      </c>
-      <c r="E24" s="2">
+      <c r="D24" s="8">
+        <v>1</v>
+      </c>
+      <c r="E24" s="8">
         <v>4</v>
       </c>
-      <c r="F24" s="2" t="s">
+      <c r="F24" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="J24" s="2"/>
-      <c r="L24" s="8" t="s">
+      <c r="G24" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="H24" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="I24" s="8"/>
+      <c r="J24" s="8"/>
+      <c r="K24" s="8"/>
+      <c r="L24" s="8"/>
+      <c r="M24" s="8"/>
+      <c r="N24" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="M24" s="8" t="s">
+      <c r="O24" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="N24" s="8" t="s">
+      <c r="P24" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="O24" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="R24" s="2">
+      <c r="Q24" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="R24" s="8"/>
+      <c r="S24" s="8"/>
+      <c r="T24" s="8">
         <v>0</v>
       </c>
-      <c r="U24" s="2" t="s">
+      <c r="U24" s="8"/>
+      <c r="V24" s="8"/>
+      <c r="W24" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="V24" s="2" t="s">
+      <c r="X24" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="W24" s="2"/>
-      <c r="X24" s="2"/>
-    </row>
-    <row r="25" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="2">
+      <c r="Y24" s="8"/>
+      <c r="Z24" s="8"/>
+    </row>
+    <row r="25" spans="1:26" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="8">
         <v>5</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="D25" s="2">
-        <v>1</v>
-      </c>
-      <c r="E25" s="2" t="s">
+      <c r="D25" s="8">
+        <v>1</v>
+      </c>
+      <c r="E25" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F25" s="2" t="s">
+      <c r="F25" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="H25" s="2" t="s">
+      <c r="G25" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="H25" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I25" s="8"/>
+      <c r="J25" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="J25" s="2"/>
-      <c r="L25" s="2"/>
-      <c r="M25" s="8" t="s">
-        <v>8</v>
-      </c>
+      <c r="K25" s="8"/>
+      <c r="L25" s="8"/>
+      <c r="M25" s="8"/>
       <c r="N25" s="8"/>
       <c r="O25" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="P25" s="2">
-        <v>1</v>
-      </c>
-      <c r="R25" s="2">
-        <v>1</v>
-      </c>
-      <c r="S25" s="2">
-        <v>1</v>
-      </c>
-      <c r="U25" s="2" t="s">
+      <c r="P25" s="8"/>
+      <c r="Q25" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="R25" s="8">
+        <v>1</v>
+      </c>
+      <c r="S25" s="8"/>
+      <c r="T25" s="8">
+        <v>1</v>
+      </c>
+      <c r="U25" s="8">
+        <v>1</v>
+      </c>
+      <c r="V25" s="8"/>
+      <c r="W25" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="V25" s="2"/>
-      <c r="W25" s="2"/>
-      <c r="X25" s="2"/>
-    </row>
-    <row r="26" spans="1:24" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="X25" s="8"/>
+      <c r="Y25" s="8"/>
+      <c r="Z25" s="8"/>
+    </row>
+    <row r="26" spans="1:26" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>6</v>
       </c>
@@ -1977,41 +2236,45 @@
       </c>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
+      <c r="H26" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="I26" s="2"/>
-      <c r="J26" s="2">
-        <v>1</v>
-      </c>
+      <c r="J26" s="2"/>
       <c r="K26" s="2"/>
-      <c r="L26" s="2"/>
-      <c r="M26" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="N26" s="8"/>
+      <c r="L26" s="2">
+        <v>1</v>
+      </c>
+      <c r="M26" s="2"/>
+      <c r="N26" s="2"/>
       <c r="O26" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="P26" s="8"/>
+      <c r="Q26" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="P26" s="4">
+      <c r="R26" s="4">
         <v>4</v>
       </c>
-      <c r="Q26" s="4"/>
-      <c r="R26" s="4">
+      <c r="S26" s="4"/>
+      <c r="T26" s="4">
         <v>2</v>
       </c>
-      <c r="S26" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="T26" s="4"/>
       <c r="U26" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="V26" s="4"/>
+      <c r="W26" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="V26" s="4" t="s">
+      <c r="X26" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="W26" s="4"/>
-      <c r="X26" s="4"/>
-    </row>
-    <row r="27" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+      <c r="Y26" s="4"/>
+      <c r="Z26" s="4"/>
+    </row>
+    <row r="27" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>7</v>
       </c>
@@ -2031,28 +2294,34 @@
         <v>90</v>
       </c>
       <c r="G27" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="I27" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="J27" s="2"/>
       <c r="L27" s="2"/>
-      <c r="M27" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="N27" s="8"/>
+      <c r="N27" s="2"/>
       <c r="O27" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="R27" s="2">
+      <c r="P27" s="8"/>
+      <c r="Q27" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="T27" s="2">
         <v>0</v>
       </c>
-      <c r="U27" s="2" t="s">
+      <c r="W27" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="V27" s="2"/>
-      <c r="W27" s="2"/>
       <c r="X27" s="2"/>
-    </row>
-    <row r="28" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+      <c r="Y27" s="2"/>
+      <c r="Z27" s="2"/>
+    </row>
+    <row r="28" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>8</v>
       </c>
@@ -2071,41 +2340,44 @@
       <c r="F28" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="J28" s="2"/>
-      <c r="K28" s="2">
+      <c r="H28" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L28" s="2"/>
+      <c r="M28" s="2">
         <v>3</v>
       </c>
-      <c r="L28" s="2">
-        <v>1</v>
-      </c>
-      <c r="M28" s="8" t="s">
+      <c r="N28" s="2">
+        <v>1</v>
+      </c>
+      <c r="O28" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="N28" s="8" t="s">
+      <c r="P28" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="O28" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q28" s="2">
-        <v>1</v>
-      </c>
-      <c r="R28" s="2">
-        <v>1</v>
-      </c>
-      <c r="S28" s="2" t="s">
-        <v>27</v>
+      <c r="Q28" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="S28" s="2">
+        <v>1</v>
+      </c>
+      <c r="T28" s="2">
+        <v>1</v>
       </c>
       <c r="U28" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="W28" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="V28" s="8" t="s">
+      <c r="X28" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="W28" s="2"/>
-      <c r="X28" s="2"/>
-    </row>
-    <row r="29" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+      <c r="Y28" s="2"/>
+      <c r="Z28" s="2"/>
+    </row>
+    <row r="29" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>9</v>
       </c>
@@ -2124,39 +2396,42 @@
       <c r="F29" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="J29" s="2"/>
-      <c r="K29" s="2">
+      <c r="H29" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L29" s="2"/>
+      <c r="M29" s="2">
         <v>2</v>
       </c>
-      <c r="L29" s="2" t="s">
+      <c r="N29" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="M29" s="8" t="s">
+      <c r="O29" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="N29" s="8" t="s">
+      <c r="P29" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="O29" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q29" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="R29" s="2" t="s">
-        <v>27</v>
+      <c r="Q29" s="8" t="s">
+        <v>8</v>
       </c>
       <c r="S29" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="T29" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="U29" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="U29" s="2" t="s">
+      <c r="W29" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="V29" s="8"/>
-      <c r="W29" s="2"/>
-      <c r="X29" s="2"/>
-    </row>
-    <row r="30" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+      <c r="X29" s="8"/>
+      <c r="Y29" s="2"/>
+      <c r="Z29" s="2"/>
+    </row>
+    <row r="30" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>10</v>
       </c>
@@ -2175,42 +2450,45 @@
       <c r="F30" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="J30" s="2"/>
-      <c r="K30" s="2">
+      <c r="H30" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L30" s="2"/>
+      <c r="M30" s="2">
         <v>3.1</v>
       </c>
-      <c r="L30" s="2" t="s">
+      <c r="N30" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="M30" s="8" t="s">
+      <c r="O30" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="N30" s="8"/>
-      <c r="O30" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="P30" s="2">
-        <v>1</v>
-      </c>
-      <c r="Q30" s="2" t="s">
+      <c r="P30" s="8"/>
+      <c r="Q30" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="R30" s="2">
+        <v>1</v>
+      </c>
+      <c r="S30" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="R30" s="2" t="s">
+      <c r="T30" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="S30" s="2" t="s">
+      <c r="U30" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="U30" s="2" t="s">
+      <c r="W30" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="V30" s="8" t="s">
+      <c r="X30" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="W30" s="2"/>
-      <c r="X30" s="2"/>
-    </row>
-    <row r="31" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+      <c r="Y30" s="2"/>
+      <c r="Z30" s="2"/>
+    </row>
+    <row r="31" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>11</v>
       </c>
@@ -2229,40 +2507,43 @@
       <c r="F31" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="G31" s="2" t="s">
+      <c r="H31" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="H31" s="2" t="s">
+      <c r="I31" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J31" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="I31" s="2" t="s">
+      <c r="K31" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="J31" s="2"/>
       <c r="L31" s="2"/>
-      <c r="M31" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="N31" s="8"/>
+      <c r="N31" s="2"/>
       <c r="O31" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="R31" s="2">
+      <c r="P31" s="8"/>
+      <c r="Q31" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="T31" s="2">
         <v>0</v>
       </c>
-      <c r="S31" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="U31" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="W31" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="V31" s="8" t="s">
+      <c r="X31" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="W31" s="2"/>
-      <c r="X31" s="2"/>
-    </row>
-    <row r="32" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+      <c r="Y31" s="2"/>
+      <c r="Z31" s="2"/>
+    </row>
+    <row r="32" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>12</v>
       </c>
@@ -2281,40 +2562,43 @@
       <c r="F32" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="J32" s="2"/>
-      <c r="K32" s="2" t="s">
+      <c r="H32" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L32" s="2"/>
+      <c r="M32" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="L32" s="2" t="s">
+      <c r="N32" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="M32" s="8" t="s">
+      <c r="O32" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="N32" s="8" t="s">
+      <c r="P32" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="O32" s="8" t="s">
-        <v>8</v>
-      </c>
       <c r="Q32" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="R32" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="S32" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S32" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="T32" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="U32" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="T32" s="3"/>
-      <c r="U32" s="2" t="s">
+      <c r="V32" s="3"/>
+      <c r="W32" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="V32" s="8"/>
-      <c r="W32" s="2"/>
-      <c r="X32" s="2"/>
-    </row>
-    <row r="33" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+      <c r="X32" s="8"/>
+      <c r="Y32" s="2"/>
+      <c r="Z32" s="2"/>
+    </row>
+    <row r="33" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>13</v>
       </c>
@@ -2334,32 +2618,38 @@
         <v>91</v>
       </c>
       <c r="G33" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="I33" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="J33" s="2" t="s">
+      <c r="L33" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="L33" s="2"/>
-      <c r="M33" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="N33" s="8"/>
+      <c r="N33" s="2"/>
       <c r="O33" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="P33" s="8"/>
+      <c r="Q33" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="R33" s="2">
+      <c r="T33" s="2">
         <v>0</v>
       </c>
-      <c r="U33" s="2" t="s">
+      <c r="W33" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="V33" s="8" t="s">
+      <c r="X33" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="W33" s="2"/>
-      <c r="X33" s="2"/>
-    </row>
-    <row r="34" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+      <c r="Y33" s="2"/>
+      <c r="Z33" s="2"/>
+    </row>
+    <row r="34" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>14</v>
       </c>
@@ -2378,32 +2668,35 @@
       <c r="F34" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="J34" s="2"/>
+      <c r="H34" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="L34" s="2"/>
-      <c r="M34" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="N34" s="8"/>
+      <c r="N34" s="2"/>
       <c r="O34" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="P34" s="2" t="s">
+      <c r="P34" s="8"/>
+      <c r="Q34" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="R34" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="R34" s="2">
+      <c r="T34" s="2">
         <v>0</v>
       </c>
-      <c r="S34" s="2">
-        <v>1</v>
-      </c>
-      <c r="U34" s="2" t="s">
+      <c r="U34" s="2">
+        <v>1</v>
+      </c>
+      <c r="W34" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="V34" s="8"/>
-      <c r="W34" s="2"/>
-      <c r="X34" s="2"/>
-    </row>
-    <row r="35" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+      <c r="X34" s="8"/>
+      <c r="Y34" s="2"/>
+      <c r="Z34" s="2"/>
+    </row>
+    <row r="35" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>15</v>
       </c>
@@ -2423,31 +2716,34 @@
         <v>89</v>
       </c>
       <c r="H35" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J35" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="J35" s="2"/>
       <c r="L35" s="2"/>
-      <c r="M35" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="N35" s="8"/>
+      <c r="N35" s="2"/>
       <c r="O35" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="R35" s="2">
-        <v>1</v>
-      </c>
-      <c r="S35" s="2" t="s">
-        <v>27</v>
+      <c r="P35" s="8"/>
+      <c r="Q35" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="T35" s="2">
+        <v>1</v>
       </c>
       <c r="U35" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="W35" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="V35" s="8"/>
-      <c r="W35" s="2"/>
-      <c r="X35" s="2"/>
-    </row>
-    <row r="36" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+      <c r="X35" s="8"/>
+      <c r="Y35" s="2"/>
+      <c r="Z35" s="2"/>
+    </row>
+    <row r="36" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>16</v>
       </c>
@@ -2466,39 +2762,42 @@
       <c r="F36" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="J36" s="2"/>
-      <c r="K36" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="L36" s="2" t="s">
+      <c r="H36" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L36" s="2"/>
+      <c r="M36" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N36" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="M36" s="8" t="s">
+      <c r="O36" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="N36" s="8" t="s">
+      <c r="P36" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="O36" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q36" s="2">
+      <c r="Q36" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="S36" s="2">
         <v>4</v>
       </c>
-      <c r="R36" s="2">
+      <c r="T36" s="2">
         <v>2</v>
       </c>
-      <c r="S36" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="U36" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="W36" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="V36" s="8"/>
-      <c r="W36" s="2"/>
-      <c r="X36" s="2"/>
-    </row>
-    <row r="37" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+      <c r="X36" s="8"/>
+      <c r="Y36" s="2"/>
+      <c r="Z36" s="2"/>
+    </row>
+    <row r="37" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>17</v>
       </c>
@@ -2518,35 +2817,38 @@
         <v>89</v>
       </c>
       <c r="H37" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J37" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="J37" s="2" t="s">
+      <c r="L37" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="L37" s="2"/>
-      <c r="M37" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="N37" s="8"/>
+      <c r="N37" s="2"/>
       <c r="O37" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="P37" s="8"/>
+      <c r="Q37" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="R37" s="8">
-        <v>1</v>
-      </c>
-      <c r="S37" s="2" t="s">
-        <v>27</v>
+      <c r="T37" s="8">
+        <v>1</v>
       </c>
       <c r="U37" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="W37" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="V37" s="8" t="s">
+      <c r="X37" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="W37" s="2"/>
-      <c r="X37" s="2"/>
-    </row>
-    <row r="38" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y37" s="2"/>
+      <c r="Z37" s="2"/>
+    </row>
+    <row r="38" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>18</v>
       </c>
@@ -2562,31 +2864,34 @@
       <c r="E38" s="2">
         <v>13</v>
       </c>
-      <c r="J38" s="2"/>
+      <c r="H38" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="L38" s="2"/>
-      <c r="M38" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="N38" s="8"/>
+      <c r="N38" s="2"/>
       <c r="O38" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="R38" s="2">
+      <c r="P38" s="8"/>
+      <c r="Q38" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="T38" s="2">
         <v>0</v>
       </c>
-      <c r="S38" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="U38" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="W38" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="V38" s="8" t="s">
+      <c r="X38" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="W38" s="2"/>
-      <c r="X38" s="2"/>
-    </row>
-    <row r="39" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y38" s="2"/>
+      <c r="Z38" s="2"/>
+    </row>
+    <row r="39" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>19</v>
       </c>
@@ -2602,639 +2907,756 @@
       <c r="E39" s="2">
         <v>15</v>
       </c>
-      <c r="J39" s="2"/>
-      <c r="L39" s="4" t="s">
+      <c r="H39" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L39" s="2"/>
+      <c r="N39" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="M39" s="3" t="s">
+      <c r="O39" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="N39" s="2"/>
-      <c r="O39" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q39" s="3">
+      <c r="P39" s="2"/>
+      <c r="Q39" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S39" s="3">
         <v>3</v>
       </c>
-      <c r="R39" s="2">
+      <c r="T39" s="2">
         <v>0</v>
       </c>
-      <c r="S39" s="2">
-        <v>1</v>
-      </c>
-      <c r="U39" s="2" t="s">
+      <c r="U39" s="2">
+        <v>1</v>
+      </c>
+      <c r="W39" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="V39" s="8"/>
-      <c r="W39" s="2"/>
-      <c r="X39" s="2"/>
-    </row>
-    <row r="40" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="X39" s="8"/>
+      <c r="Y39" s="2"/>
+      <c r="Z39" s="2"/>
+    </row>
+    <row r="40" spans="1:26" x14ac:dyDescent="0.25">
       <c r="D40" s="1"/>
       <c r="E40" s="1"/>
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
+      <c r="J40" s="1"/>
       <c r="K40" s="1"/>
-      <c r="L40" s="1"/>
-      <c r="V40" s="7"/>
-    </row>
-    <row r="41" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="M40" s="1"/>
+      <c r="N40" s="1"/>
+      <c r="X40" s="7"/>
+    </row>
+    <row r="41" spans="1:26" x14ac:dyDescent="0.25">
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
       <c r="F41" s="1"/>
       <c r="G41" s="1"/>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
+      <c r="J41" s="1"/>
       <c r="K41" s="1"/>
-      <c r="L41" s="1"/>
-      <c r="V41" s="7"/>
-    </row>
-    <row r="42" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="M41" s="1"/>
+      <c r="N41" s="1"/>
+      <c r="X41" s="7"/>
+    </row>
+    <row r="42" spans="1:26" x14ac:dyDescent="0.25">
       <c r="D42" s="1"/>
       <c r="E42" s="1"/>
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
+      <c r="J42" s="1"/>
       <c r="K42" s="1"/>
-      <c r="L42" s="1"/>
-      <c r="V42" s="7"/>
-    </row>
-    <row r="43" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="M42" s="1"/>
+      <c r="N42" s="1"/>
+      <c r="X42" s="7"/>
+    </row>
+    <row r="43" spans="1:26" x14ac:dyDescent="0.25">
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
+      <c r="J43" s="1"/>
       <c r="K43" s="1"/>
-      <c r="L43" s="1"/>
-      <c r="V43" s="7"/>
-    </row>
-    <row r="44" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="M43" s="1"/>
+      <c r="N43" s="1"/>
+      <c r="X43" s="7"/>
+    </row>
+    <row r="44" spans="1:26" x14ac:dyDescent="0.25">
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
       <c r="F44" s="1"/>
       <c r="G44" s="1"/>
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
+      <c r="J44" s="1"/>
       <c r="K44" s="1"/>
-      <c r="L44" s="1"/>
-    </row>
-    <row r="45" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="M44" s="1"/>
+      <c r="N44" s="1"/>
+    </row>
+    <row r="45" spans="1:26" x14ac:dyDescent="0.25">
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
       <c r="G45" s="1"/>
       <c r="H45" s="1"/>
       <c r="I45" s="1"/>
+      <c r="J45" s="1"/>
       <c r="K45" s="1"/>
-      <c r="L45" s="1"/>
-    </row>
-    <row r="46" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="M45" s="1"/>
+      <c r="N45" s="1"/>
+    </row>
+    <row r="46" spans="1:26" x14ac:dyDescent="0.25">
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
       <c r="F46" s="1"/>
       <c r="G46" s="1"/>
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
+      <c r="J46" s="1"/>
       <c r="K46" s="1"/>
-      <c r="L46" s="1"/>
-    </row>
-    <row r="47" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="M46" s="1"/>
+      <c r="N46" s="1"/>
+    </row>
+    <row r="47" spans="1:26" x14ac:dyDescent="0.25">
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
       <c r="F47" s="1"/>
       <c r="G47" s="1"/>
       <c r="H47" s="1"/>
       <c r="I47" s="1"/>
+      <c r="J47" s="1"/>
       <c r="K47" s="1"/>
-      <c r="L47" s="1"/>
-    </row>
-    <row r="48" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="M47" s="1"/>
+      <c r="N47" s="1"/>
+    </row>
+    <row r="48" spans="1:26" x14ac:dyDescent="0.25">
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
       <c r="F48" s="1"/>
       <c r="G48" s="1"/>
       <c r="H48" s="1"/>
       <c r="I48" s="1"/>
+      <c r="J48" s="1"/>
       <c r="K48" s="1"/>
-      <c r="L48" s="1"/>
-    </row>
-    <row r="49" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="M48" s="1"/>
+      <c r="N48" s="1"/>
+    </row>
+    <row r="49" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D49" s="1"/>
       <c r="E49" s="1"/>
       <c r="F49" s="1"/>
       <c r="G49" s="1"/>
       <c r="H49" s="1"/>
       <c r="I49" s="1"/>
+      <c r="J49" s="1"/>
       <c r="K49" s="1"/>
-      <c r="L49" s="1"/>
-    </row>
-    <row r="50" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="M49" s="1"/>
+      <c r="N49" s="1"/>
+    </row>
+    <row r="50" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D50" s="1"/>
       <c r="E50" s="1"/>
       <c r="F50" s="1"/>
       <c r="G50" s="1"/>
       <c r="H50" s="1"/>
       <c r="I50" s="1"/>
+      <c r="J50" s="1"/>
       <c r="K50" s="1"/>
-      <c r="L50" s="1"/>
-    </row>
-    <row r="51" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="M50" s="1"/>
+      <c r="N50" s="1"/>
+    </row>
+    <row r="51" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D51" s="1"/>
       <c r="E51" s="1"/>
       <c r="F51" s="1"/>
       <c r="G51" s="1"/>
       <c r="H51" s="1"/>
       <c r="I51" s="1"/>
+      <c r="J51" s="1"/>
       <c r="K51" s="1"/>
-      <c r="L51" s="1"/>
-    </row>
-    <row r="52" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="M51" s="1"/>
+      <c r="N51" s="1"/>
+    </row>
+    <row r="52" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D52" s="1"/>
       <c r="E52" s="1"/>
       <c r="F52" s="1"/>
       <c r="G52" s="1"/>
       <c r="H52" s="1"/>
       <c r="I52" s="1"/>
+      <c r="J52" s="1"/>
       <c r="K52" s="1"/>
-      <c r="L52" s="1"/>
-    </row>
-    <row r="53" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="M52" s="1"/>
+      <c r="N52" s="1"/>
+    </row>
+    <row r="53" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
       <c r="F53" s="1"/>
       <c r="G53" s="1"/>
       <c r="H53" s="1"/>
       <c r="I53" s="1"/>
+      <c r="J53" s="1"/>
       <c r="K53" s="1"/>
-      <c r="L53" s="1"/>
-    </row>
-    <row r="54" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="M53" s="1"/>
+      <c r="N53" s="1"/>
+    </row>
+    <row r="54" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D54" s="1"/>
       <c r="E54" s="1"/>
       <c r="F54" s="1"/>
       <c r="G54" s="1"/>
       <c r="H54" s="1"/>
       <c r="I54" s="1"/>
+      <c r="J54" s="1"/>
       <c r="K54" s="1"/>
-      <c r="L54" s="1"/>
-    </row>
-    <row r="55" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="M54" s="1"/>
+      <c r="N54" s="1"/>
+    </row>
+    <row r="55" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D55" s="1"/>
       <c r="E55" s="1"/>
       <c r="F55" s="1"/>
       <c r="G55" s="1"/>
       <c r="H55" s="1"/>
       <c r="I55" s="1"/>
+      <c r="J55" s="1"/>
       <c r="K55" s="1"/>
-      <c r="L55" s="1"/>
-    </row>
-    <row r="56" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="M55" s="1"/>
+      <c r="N55" s="1"/>
+    </row>
+    <row r="56" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D56" s="1"/>
       <c r="E56" s="1"/>
       <c r="F56" s="1"/>
       <c r="G56" s="1"/>
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
+      <c r="J56" s="1"/>
       <c r="K56" s="1"/>
-      <c r="L56" s="1"/>
-    </row>
-    <row r="57" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="M56" s="1"/>
+      <c r="N56" s="1"/>
+    </row>
+    <row r="57" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D57" s="1"/>
       <c r="E57" s="1"/>
       <c r="F57" s="1"/>
       <c r="G57" s="1"/>
       <c r="H57" s="1"/>
       <c r="I57" s="1"/>
+      <c r="J57" s="1"/>
       <c r="K57" s="1"/>
-      <c r="L57" s="1"/>
-    </row>
-    <row r="58" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="M57" s="1"/>
+      <c r="N57" s="1"/>
+    </row>
+    <row r="58" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D58" s="1"/>
       <c r="E58" s="1"/>
       <c r="F58" s="1"/>
       <c r="G58" s="1"/>
       <c r="H58" s="1"/>
       <c r="I58" s="1"/>
+      <c r="J58" s="1"/>
       <c r="K58" s="1"/>
-      <c r="L58" s="1"/>
-    </row>
-    <row r="59" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="M58" s="1"/>
+      <c r="N58" s="1"/>
+    </row>
+    <row r="59" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D59" s="1"/>
       <c r="E59" s="1"/>
       <c r="F59" s="1"/>
       <c r="G59" s="1"/>
       <c r="H59" s="1"/>
       <c r="I59" s="1"/>
+      <c r="J59" s="1"/>
       <c r="K59" s="1"/>
-      <c r="L59" s="1"/>
-    </row>
-    <row r="60" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="M59" s="1"/>
+      <c r="N59" s="1"/>
+    </row>
+    <row r="60" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D60" s="1"/>
       <c r="E60" s="1"/>
       <c r="F60" s="1"/>
       <c r="G60" s="1"/>
       <c r="H60" s="1"/>
       <c r="I60" s="1"/>
+      <c r="J60" s="1"/>
       <c r="K60" s="1"/>
-      <c r="L60" s="1"/>
-    </row>
-    <row r="61" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="M60" s="1"/>
+      <c r="N60" s="1"/>
+    </row>
+    <row r="61" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D61" s="1"/>
       <c r="E61" s="1"/>
       <c r="F61" s="1"/>
       <c r="G61" s="1"/>
       <c r="H61" s="1"/>
       <c r="I61" s="1"/>
+      <c r="J61" s="1"/>
       <c r="K61" s="1"/>
-      <c r="L61" s="1"/>
-    </row>
-    <row r="62" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="M61" s="1"/>
+      <c r="N61" s="1"/>
+    </row>
+    <row r="62" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D62" s="1"/>
       <c r="E62" s="1"/>
       <c r="F62" s="1"/>
       <c r="G62" s="1"/>
       <c r="H62" s="1"/>
       <c r="I62" s="1"/>
+      <c r="J62" s="1"/>
       <c r="K62" s="1"/>
-      <c r="L62" s="1"/>
-    </row>
-    <row r="63" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="M62" s="1"/>
+      <c r="N62" s="1"/>
+    </row>
+    <row r="63" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D63" s="1"/>
       <c r="E63" s="1"/>
       <c r="F63" s="1"/>
       <c r="G63" s="1"/>
       <c r="H63" s="1"/>
       <c r="I63" s="1"/>
+      <c r="J63" s="1"/>
       <c r="K63" s="1"/>
-      <c r="L63" s="1"/>
-    </row>
-    <row r="64" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="M63" s="1"/>
+      <c r="N63" s="1"/>
+    </row>
+    <row r="64" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D64" s="1"/>
       <c r="E64" s="1"/>
       <c r="F64" s="1"/>
       <c r="G64" s="1"/>
       <c r="H64" s="1"/>
       <c r="I64" s="1"/>
+      <c r="J64" s="1"/>
       <c r="K64" s="1"/>
-      <c r="L64" s="1"/>
-    </row>
-    <row r="65" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="M64" s="1"/>
+      <c r="N64" s="1"/>
+    </row>
+    <row r="65" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D65" s="1"/>
       <c r="E65" s="1"/>
       <c r="F65" s="1"/>
       <c r="G65" s="1"/>
       <c r="H65" s="1"/>
       <c r="I65" s="1"/>
+      <c r="J65" s="1"/>
       <c r="K65" s="1"/>
-      <c r="L65" s="1"/>
-    </row>
-    <row r="66" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="M65" s="1"/>
+      <c r="N65" s="1"/>
+    </row>
+    <row r="66" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D66" s="1"/>
       <c r="E66" s="1"/>
       <c r="F66" s="1"/>
       <c r="G66" s="1"/>
       <c r="H66" s="1"/>
       <c r="I66" s="1"/>
+      <c r="J66" s="1"/>
       <c r="K66" s="1"/>
-      <c r="L66" s="1"/>
-    </row>
-    <row r="67" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="M66" s="1"/>
+      <c r="N66" s="1"/>
+    </row>
+    <row r="67" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D67" s="1"/>
       <c r="E67" s="1"/>
       <c r="F67" s="1"/>
       <c r="G67" s="1"/>
       <c r="H67" s="1"/>
       <c r="I67" s="1"/>
+      <c r="J67" s="1"/>
       <c r="K67" s="1"/>
-      <c r="L67" s="1"/>
-    </row>
-    <row r="68" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="M67" s="1"/>
+      <c r="N67" s="1"/>
+    </row>
+    <row r="68" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D68" s="1"/>
       <c r="E68" s="1"/>
       <c r="F68" s="1"/>
       <c r="G68" s="1"/>
       <c r="H68" s="1"/>
       <c r="I68" s="1"/>
+      <c r="J68" s="1"/>
       <c r="K68" s="1"/>
-      <c r="L68" s="1"/>
-    </row>
-    <row r="69" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="M68" s="1"/>
+      <c r="N68" s="1"/>
+    </row>
+    <row r="69" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D69" s="1"/>
       <c r="E69" s="1"/>
       <c r="F69" s="1"/>
       <c r="G69" s="1"/>
       <c r="H69" s="1"/>
       <c r="I69" s="1"/>
+      <c r="J69" s="1"/>
       <c r="K69" s="1"/>
-      <c r="L69" s="1"/>
-    </row>
-    <row r="70" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="M69" s="1"/>
+      <c r="N69" s="1"/>
+    </row>
+    <row r="70" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D70" s="1"/>
       <c r="E70" s="1"/>
       <c r="F70" s="1"/>
       <c r="G70" s="1"/>
       <c r="H70" s="1"/>
       <c r="I70" s="1"/>
+      <c r="J70" s="1"/>
       <c r="K70" s="1"/>
-      <c r="L70" s="1"/>
-    </row>
-    <row r="71" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="M70" s="1"/>
+      <c r="N70" s="1"/>
+    </row>
+    <row r="71" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D71" s="1"/>
       <c r="E71" s="1"/>
       <c r="F71" s="1"/>
       <c r="G71" s="1"/>
       <c r="H71" s="1"/>
       <c r="I71" s="1"/>
+      <c r="J71" s="1"/>
       <c r="K71" s="1"/>
-      <c r="L71" s="1"/>
-    </row>
-    <row r="72" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="M71" s="1"/>
+      <c r="N71" s="1"/>
+    </row>
+    <row r="72" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D72" s="1"/>
       <c r="E72" s="1"/>
       <c r="F72" s="1"/>
       <c r="G72" s="1"/>
       <c r="H72" s="1"/>
       <c r="I72" s="1"/>
+      <c r="J72" s="1"/>
       <c r="K72" s="1"/>
-      <c r="L72" s="1"/>
-    </row>
-    <row r="73" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="M72" s="1"/>
+      <c r="N72" s="1"/>
+    </row>
+    <row r="73" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D73" s="1"/>
       <c r="E73" s="1"/>
       <c r="F73" s="1"/>
       <c r="G73" s="1"/>
       <c r="H73" s="1"/>
       <c r="I73" s="1"/>
+      <c r="J73" s="1"/>
       <c r="K73" s="1"/>
-      <c r="L73" s="1"/>
-    </row>
-    <row r="74" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="M73" s="1"/>
+      <c r="N73" s="1"/>
+    </row>
+    <row r="74" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D74" s="1"/>
       <c r="E74" s="1"/>
       <c r="F74" s="1"/>
       <c r="G74" s="1"/>
       <c r="H74" s="1"/>
       <c r="I74" s="1"/>
+      <c r="J74" s="1"/>
       <c r="K74" s="1"/>
-      <c r="L74" s="1"/>
-    </row>
-    <row r="75" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="M74" s="1"/>
+      <c r="N74" s="1"/>
+    </row>
+    <row r="75" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D75" s="1"/>
       <c r="E75" s="1"/>
       <c r="F75" s="1"/>
       <c r="G75" s="1"/>
       <c r="H75" s="1"/>
       <c r="I75" s="1"/>
+      <c r="J75" s="1"/>
       <c r="K75" s="1"/>
-      <c r="L75" s="1"/>
-    </row>
-    <row r="76" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="M75" s="1"/>
+      <c r="N75" s="1"/>
+    </row>
+    <row r="76" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D76" s="1"/>
       <c r="E76" s="1"/>
       <c r="F76" s="1"/>
       <c r="G76" s="1"/>
       <c r="H76" s="1"/>
       <c r="I76" s="1"/>
+      <c r="J76" s="1"/>
       <c r="K76" s="1"/>
-      <c r="L76" s="1"/>
-    </row>
-    <row r="77" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="M76" s="1"/>
+      <c r="N76" s="1"/>
+    </row>
+    <row r="77" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D77" s="1"/>
       <c r="E77" s="1"/>
       <c r="F77" s="1"/>
       <c r="G77" s="1"/>
       <c r="H77" s="1"/>
       <c r="I77" s="1"/>
+      <c r="J77" s="1"/>
       <c r="K77" s="1"/>
-      <c r="L77" s="1"/>
-    </row>
-    <row r="78" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="M77" s="1"/>
+      <c r="N77" s="1"/>
+    </row>
+    <row r="78" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D78" s="1"/>
       <c r="E78" s="1"/>
       <c r="F78" s="1"/>
       <c r="G78" s="1"/>
       <c r="H78" s="1"/>
       <c r="I78" s="1"/>
+      <c r="J78" s="1"/>
       <c r="K78" s="1"/>
-      <c r="L78" s="1"/>
-    </row>
-    <row r="79" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="M78" s="1"/>
+      <c r="N78" s="1"/>
+    </row>
+    <row r="79" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D79" s="1"/>
       <c r="E79" s="1"/>
       <c r="F79" s="1"/>
       <c r="G79" s="1"/>
       <c r="H79" s="1"/>
       <c r="I79" s="1"/>
+      <c r="J79" s="1"/>
       <c r="K79" s="1"/>
-      <c r="L79" s="1"/>
-    </row>
-    <row r="80" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="M79" s="1"/>
+      <c r="N79" s="1"/>
+    </row>
+    <row r="80" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D80" s="1"/>
       <c r="E80" s="1"/>
       <c r="F80" s="1"/>
       <c r="G80" s="1"/>
       <c r="H80" s="1"/>
       <c r="I80" s="1"/>
+      <c r="J80" s="1"/>
       <c r="K80" s="1"/>
-      <c r="L80" s="1"/>
-    </row>
-    <row r="81" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="M80" s="1"/>
+      <c r="N80" s="1"/>
+    </row>
+    <row r="81" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D81" s="1"/>
       <c r="E81" s="1"/>
       <c r="F81" s="1"/>
       <c r="G81" s="1"/>
       <c r="H81" s="1"/>
       <c r="I81" s="1"/>
+      <c r="J81" s="1"/>
       <c r="K81" s="1"/>
-      <c r="L81" s="1"/>
-    </row>
-    <row r="82" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="M81" s="1"/>
+      <c r="N81" s="1"/>
+    </row>
+    <row r="82" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D82" s="1"/>
       <c r="E82" s="1"/>
       <c r="F82" s="1"/>
       <c r="G82" s="1"/>
       <c r="H82" s="1"/>
       <c r="I82" s="1"/>
+      <c r="J82" s="1"/>
       <c r="K82" s="1"/>
-      <c r="L82" s="1"/>
-    </row>
-    <row r="83" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="M82" s="1"/>
+      <c r="N82" s="1"/>
+    </row>
+    <row r="83" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D83" s="1"/>
       <c r="E83" s="1"/>
       <c r="F83" s="1"/>
       <c r="G83" s="1"/>
       <c r="H83" s="1"/>
       <c r="I83" s="1"/>
+      <c r="J83" s="1"/>
       <c r="K83" s="1"/>
-      <c r="L83" s="1"/>
-    </row>
-    <row r="84" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="M83" s="1"/>
+      <c r="N83" s="1"/>
+    </row>
+    <row r="84" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D84" s="1"/>
       <c r="E84" s="1"/>
       <c r="F84" s="1"/>
       <c r="G84" s="1"/>
       <c r="H84" s="1"/>
       <c r="I84" s="1"/>
+      <c r="J84" s="1"/>
       <c r="K84" s="1"/>
-      <c r="L84" s="1"/>
-    </row>
-    <row r="85" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="M84" s="1"/>
+      <c r="N84" s="1"/>
+    </row>
+    <row r="85" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D85" s="1"/>
       <c r="E85" s="1"/>
       <c r="F85" s="1"/>
       <c r="G85" s="1"/>
       <c r="H85" s="1"/>
       <c r="I85" s="1"/>
+      <c r="J85" s="1"/>
       <c r="K85" s="1"/>
-      <c r="L85" s="1"/>
-    </row>
-    <row r="86" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="M85" s="1"/>
+      <c r="N85" s="1"/>
+    </row>
+    <row r="86" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D86" s="1"/>
       <c r="E86" s="1"/>
       <c r="F86" s="1"/>
       <c r="G86" s="1"/>
       <c r="H86" s="1"/>
       <c r="I86" s="1"/>
+      <c r="J86" s="1"/>
       <c r="K86" s="1"/>
-      <c r="L86" s="1"/>
-    </row>
-    <row r="87" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="M86" s="1"/>
+      <c r="N86" s="1"/>
+    </row>
+    <row r="87" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D87" s="1"/>
       <c r="E87" s="1"/>
       <c r="F87" s="1"/>
       <c r="G87" s="1"/>
       <c r="H87" s="1"/>
       <c r="I87" s="1"/>
+      <c r="J87" s="1"/>
       <c r="K87" s="1"/>
-      <c r="L87" s="1"/>
-    </row>
-    <row r="88" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="M87" s="1"/>
+      <c r="N87" s="1"/>
+    </row>
+    <row r="88" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D88" s="1"/>
       <c r="E88" s="1"/>
       <c r="F88" s="1"/>
       <c r="G88" s="1"/>
       <c r="H88" s="1"/>
       <c r="I88" s="1"/>
+      <c r="J88" s="1"/>
       <c r="K88" s="1"/>
-      <c r="L88" s="1"/>
-    </row>
-    <row r="89" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="M88" s="1"/>
+      <c r="N88" s="1"/>
+    </row>
+    <row r="89" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D89" s="1"/>
       <c r="E89" s="1"/>
       <c r="F89" s="1"/>
       <c r="G89" s="1"/>
       <c r="H89" s="1"/>
       <c r="I89" s="1"/>
+      <c r="J89" s="1"/>
       <c r="K89" s="1"/>
-      <c r="L89" s="1"/>
-    </row>
-    <row r="90" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="M89" s="1"/>
+      <c r="N89" s="1"/>
+    </row>
+    <row r="90" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D90" s="1"/>
       <c r="E90" s="1"/>
       <c r="F90" s="1"/>
       <c r="G90" s="1"/>
       <c r="H90" s="1"/>
       <c r="I90" s="1"/>
+      <c r="J90" s="1"/>
       <c r="K90" s="1"/>
-      <c r="L90" s="1"/>
-    </row>
-    <row r="91" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="M90" s="1"/>
+      <c r="N90" s="1"/>
+    </row>
+    <row r="91" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D91" s="1"/>
       <c r="E91" s="1"/>
       <c r="F91" s="1"/>
       <c r="G91" s="1"/>
       <c r="H91" s="1"/>
       <c r="I91" s="1"/>
+      <c r="J91" s="1"/>
       <c r="K91" s="1"/>
-      <c r="L91" s="1"/>
-    </row>
-    <row r="92" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="M91" s="1"/>
+      <c r="N91" s="1"/>
+    </row>
+    <row r="92" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D92" s="1"/>
       <c r="E92" s="1"/>
       <c r="F92" s="1"/>
       <c r="G92" s="1"/>
       <c r="H92" s="1"/>
       <c r="I92" s="1"/>
+      <c r="J92" s="1"/>
       <c r="K92" s="1"/>
-      <c r="L92" s="1"/>
-    </row>
-    <row r="93" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="M92" s="1"/>
+      <c r="N92" s="1"/>
+    </row>
+    <row r="93" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D93" s="1"/>
       <c r="E93" s="1"/>
       <c r="F93" s="1"/>
       <c r="G93" s="1"/>
       <c r="H93" s="1"/>
       <c r="I93" s="1"/>
+      <c r="J93" s="1"/>
       <c r="K93" s="1"/>
-      <c r="L93" s="1"/>
-    </row>
-    <row r="94" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="M93" s="1"/>
+      <c r="N93" s="1"/>
+    </row>
+    <row r="94" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D94" s="1"/>
       <c r="E94" s="1"/>
       <c r="F94" s="1"/>
       <c r="G94" s="1"/>
       <c r="H94" s="1"/>
       <c r="I94" s="1"/>
+      <c r="J94" s="1"/>
       <c r="K94" s="1"/>
-      <c r="L94" s="1"/>
-    </row>
-    <row r="95" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="M94" s="1"/>
+      <c r="N94" s="1"/>
+    </row>
+    <row r="95" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D95" s="1"/>
       <c r="E95" s="1"/>
       <c r="F95" s="1"/>
       <c r="G95" s="1"/>
       <c r="H95" s="1"/>
       <c r="I95" s="1"/>
+      <c r="J95" s="1"/>
       <c r="K95" s="1"/>
-      <c r="L95" s="1"/>
-    </row>
-    <row r="96" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="M95" s="1"/>
+      <c r="N95" s="1"/>
+    </row>
+    <row r="96" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D96" s="1"/>
       <c r="E96" s="1"/>
       <c r="F96" s="1"/>
       <c r="G96" s="1"/>
       <c r="H96" s="1"/>
       <c r="I96" s="1"/>
+      <c r="J96" s="1"/>
       <c r="K96" s="1"/>
-      <c r="L96" s="1"/>
-    </row>
-    <row r="97" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="M96" s="1"/>
+      <c r="N96" s="1"/>
+    </row>
+    <row r="97" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D97" s="1"/>
       <c r="E97" s="1"/>
       <c r="F97" s="1"/>
       <c r="G97" s="1"/>
       <c r="H97" s="1"/>
       <c r="I97" s="1"/>
+      <c r="J97" s="1"/>
       <c r="K97" s="1"/>
-      <c r="L97" s="1"/>
-    </row>
-    <row r="98" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="M97" s="1"/>
+      <c r="N97" s="1"/>
+    </row>
+    <row r="98" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D98" s="1"/>
       <c r="E98" s="1"/>
       <c r="F98" s="1"/>
       <c r="G98" s="1"/>
       <c r="H98" s="1"/>
       <c r="I98" s="1"/>
+      <c r="J98" s="1"/>
       <c r="K98" s="1"/>
-      <c r="L98" s="1"/>
+      <c r="M98" s="1"/>
+      <c r="N98" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V98" xr:uid="{E5603586-01B1-45C3-888E-EC2BF5D85650}">
-    <filterColumn colId="5">
-      <filters blank="1"/>
-    </filterColumn>
-  </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B21:V39">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B21:X39">
     <sortCondition ref="D21:D39"/>
     <sortCondition ref="E21:E39"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Dane/karty_v1.xlsx
+++ b/Dane/karty_v1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a40667ca9a5261e0/Dokumenty/Dokumenty/Gra Walka o Dusze/Symulator/Dane/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="116" documentId="8_{C60639C0-3DC1-46DF-8FF5-DD98044E12E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{80763C81-E1F9-420E-B8B9-DDA2F3FD6DC3}"/>
+  <xr:revisionPtr revIDLastSave="224" documentId="8_{C60639C0-3DC1-46DF-8FF5-DD98044E12E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{662FDB3F-4B7A-4C79-B4B9-EAB38EAF43D3}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1C612D17-AB6F-4FCE-AA6C-1D2201D34FB7}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Arkusz1!$A$1:$X$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Arkusz1!$A$1:$Z$98</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,6 +33,55 @@
     <author>Mariusz Janeczko</author>
   </authors>
   <commentList>
+    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{F7200FBB-9721-4E27-803F-57F6C2399E04}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Mariusz Janeczko:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+musi być warunkowa 
+b- oznacza brak warunku</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N12" authorId="0" shapeId="0" xr:uid="{9ED59B26-42DD-43C9-842D-3AE9CA821EE5}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Mariusz Janeczko:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+trzy użycia czyli wszyscy na arenie</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="H15" authorId="0" shapeId="0" xr:uid="{99EB7673-5FD0-4BC1-9BA0-E90A43A21D65}">
       <text>
         <r>
@@ -55,11 +104,35 @@
             <charset val="238"/>
           </rPr>
           <t xml:space="preserve">
-ZYCIE - zdolnosc nr 1 to ocalenie przeciwnika, dolnosc nr 2 to zabicie śmierci</t>
+ZYCIE - zdolnosc nr 1 to ocalenie przeciwnika</t>
         </r>
       </text>
     </comment>
-    <comment ref="H34" authorId="0" shapeId="0" xr:uid="{A6E5B52D-9858-4032-ADC8-5AB9224B7549}">
+    <comment ref="N29" authorId="0" shapeId="0" xr:uid="{3E0F4ED4-DC85-46A7-96AF-8D43B26507BE}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Mariusz Janeczko:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+1 użycie czyli tylko jeden sojusznik po tobie</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H35" authorId="0" shapeId="0" xr:uid="{A6E5B52D-9858-4032-ADC8-5AB9224B7549}">
       <text>
         <r>
           <rPr>
@@ -90,7 +163,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="103">
   <si>
     <t>klasa</t>
   </si>
@@ -365,9 +438,6 @@
     <t>brak</t>
   </si>
   <si>
-    <t>F</t>
-  </si>
-  <si>
     <t>klasa_wroga&lt;</t>
   </si>
   <si>
@@ -384,13 +454,31 @@
   </si>
   <si>
     <t>b</t>
+  </si>
+  <si>
+    <t>ok all</t>
+  </si>
+  <si>
+    <t>2K2</t>
+  </si>
+  <si>
+    <t>klasa_wroga&lt;=</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>Duch Łaski</t>
+  </si>
+  <si>
+    <t>Terror</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
@@ -452,6 +540,43 @@
       <family val="2"/>
       <charset val="238"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="7"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0" tint="-4.9989318521683403E-2"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF6D6D"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -467,7 +592,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -490,11 +615,76 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF454545"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF454545"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF454545"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF454545"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF454545"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF454545"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF454545"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF454545"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF454545"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF454545"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF454545"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF454545"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF454545"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -512,6 +702,65 @@
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -877,10 +1126,10 @@
         <v>88</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>80</v>
@@ -949,6 +1198,9 @@
       </c>
       <c r="F2" s="2" t="s">
         <v>89</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>97</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>27</v>
@@ -996,7 +1248,7 @@
         <v>89</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H3" s="8" t="s">
         <v>27</v>
@@ -1054,7 +1306,7 @@
         <v>89</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H4" s="8" t="s">
         <v>27</v>
@@ -1112,7 +1364,7 @@
         <v>90</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H5" s="8" t="s">
         <v>54</v>
@@ -1121,7 +1373,9 @@
         <v>87</v>
       </c>
       <c r="J5" s="8"/>
-      <c r="K5" s="8"/>
+      <c r="K5" s="8" t="s">
+        <v>96</v>
+      </c>
       <c r="L5" s="8"/>
       <c r="M5" s="8"/>
       <c r="N5" s="8"/>
@@ -1168,7 +1422,7 @@
         <v>90</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H6" s="8" t="s">
         <v>54</v>
@@ -1223,11 +1477,14 @@
       <c r="F7" s="2" t="s">
         <v>89</v>
       </c>
+      <c r="G7" s="2" t="s">
+        <v>95</v>
+      </c>
       <c r="H7" s="2" t="s">
         <v>27</v>
       </c>
       <c r="L7" s="2"/>
-      <c r="M7" s="2" t="s">
+      <c r="M7" s="9" t="s">
         <v>27</v>
       </c>
       <c r="N7" s="2" t="s">
@@ -1276,13 +1533,13 @@
       <c r="F8" s="2" t="s">
         <v>89</v>
       </c>
+      <c r="G8" s="2" t="s">
+        <v>95</v>
+      </c>
       <c r="H8" s="2" t="s">
         <v>27</v>
       </c>
       <c r="L8" s="2"/>
-      <c r="M8" s="2" t="s">
-        <v>21</v>
-      </c>
       <c r="N8" s="2" t="s">
         <v>21</v>
       </c>
@@ -1327,6 +1584,9 @@
       <c r="F9" s="2" t="s">
         <v>89</v>
       </c>
+      <c r="G9" s="2" t="s">
+        <v>95</v>
+      </c>
       <c r="H9" s="2" t="s">
         <v>27</v>
       </c>
@@ -1383,6 +1643,9 @@
       <c r="F10" s="2" t="s">
         <v>89</v>
       </c>
+      <c r="G10" s="2" t="s">
+        <v>95</v>
+      </c>
       <c r="H10" s="2" t="s">
         <v>27</v>
       </c>
@@ -1441,6 +1704,9 @@
       <c r="F11" s="2" t="s">
         <v>89</v>
       </c>
+      <c r="G11" s="2" t="s">
+        <v>95</v>
+      </c>
       <c r="H11" s="2" t="s">
         <v>27</v>
       </c>
@@ -1493,14 +1759,20 @@
       <c r="F12" s="2" t="s">
         <v>89</v>
       </c>
+      <c r="G12" s="2" t="s">
+        <v>95</v>
+      </c>
       <c r="H12" s="2" t="s">
         <v>27</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>87</v>
       </c>
+      <c r="K12" s="2" t="s">
+        <v>96</v>
+      </c>
       <c r="L12" s="2"/>
-      <c r="M12" s="4" t="s">
+      <c r="M12" s="8" t="s">
         <v>87</v>
       </c>
       <c r="N12" s="2" t="s">
@@ -1546,13 +1818,13 @@
       <c r="E13" s="2">
         <v>10</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="F13" s="13" t="s">
         <v>89</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="H13" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H13" s="10" t="s">
         <v>27</v>
       </c>
       <c r="J13" s="2" t="s">
@@ -1596,17 +1868,20 @@
       <c r="E14" s="2">
         <v>11</v>
       </c>
-      <c r="F14" s="2" t="s">
-        <v>91</v>
+      <c r="F14" s="13" t="s">
+        <v>89</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>54</v>
+        <v>95</v>
+      </c>
+      <c r="H14" s="10" t="s">
+        <v>27</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>23</v>
+        <v>87</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>23</v>
@@ -1653,11 +1928,14 @@
       <c r="E15" s="2">
         <v>12</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="F15" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="H15" s="2" t="s">
-        <v>23</v>
+      <c r="G15" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H15" s="10" t="s">
+        <v>27</v>
       </c>
       <c r="L15" s="2"/>
       <c r="N15" s="2"/>
@@ -1699,15 +1977,20 @@
       <c r="E16" s="2">
         <v>13</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="F16" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="H16" s="2" t="s">
+      <c r="G16" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H16" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="L16" s="2"/>
+      <c r="L16" s="2" t="s">
+        <v>23</v>
+      </c>
       <c r="M16" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="N16" s="2" t="s">
         <v>71</v>
@@ -1715,7 +1998,9 @@
       <c r="O16" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="P16" s="8"/>
+      <c r="P16" s="8" t="s">
+        <v>96</v>
+      </c>
       <c r="Q16" s="8" t="s">
         <v>7</v>
       </c>
@@ -1747,13 +2032,16 @@
       <c r="D17" s="2">
         <v>4</v>
       </c>
-      <c r="E17" s="2">
+      <c r="E17" s="8">
         <v>14</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="F17" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="H17" s="2" t="s">
+      <c r="G17" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H17" s="10" t="s">
         <v>27</v>
       </c>
       <c r="I17" s="2" t="s">
@@ -1790,10 +2078,10 @@
       <c r="Z17" s="2"/>
     </row>
     <row r="18" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A18" s="2">
+      <c r="A18" s="8">
         <v>17</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="8" t="s">
         <v>30</v>
       </c>
       <c r="C18" s="2" t="s">
@@ -1802,13 +2090,16 @@
       <c r="D18" s="2">
         <v>5</v>
       </c>
-      <c r="E18" s="2">
+      <c r="E18" s="8">
         <v>13</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="F18" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="H18" s="2" t="s">
+      <c r="G18" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H18" s="10" t="s">
         <v>27</v>
       </c>
       <c r="J18" s="2" t="s">
@@ -1840,10 +2131,10 @@
       <c r="Z18" s="2"/>
     </row>
     <row r="19" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A19" s="2">
+      <c r="A19" s="8">
         <v>18</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="8" t="s">
         <v>14</v>
       </c>
       <c r="C19" s="2" t="s">
@@ -1852,23 +2143,23 @@
       <c r="D19" s="2">
         <v>5</v>
       </c>
-      <c r="E19" s="2">
-        <v>15</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>91</v>
+      <c r="E19" s="26">
+        <v>16</v>
+      </c>
+      <c r="F19" s="13" t="s">
+        <v>90</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="H19" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="H19" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="I19" s="2" t="s">
-        <v>15</v>
+      <c r="K19" s="2" t="s">
+        <v>96</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>15</v>
+        <v>98</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="8" t="s">
@@ -1889,10 +2180,10 @@
       <c r="Z19" s="2"/>
     </row>
     <row r="20" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A20" s="2">
+      <c r="A20" s="8">
         <v>19</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="8" t="s">
         <v>3</v>
       </c>
       <c r="C20" s="2" t="s">
@@ -1901,17 +2192,14 @@
       <c r="D20" s="2">
         <v>5</v>
       </c>
-      <c r="E20" s="2">
+      <c r="E20" s="27">
         <v>99</v>
       </c>
-      <c r="F20" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>54</v>
+      <c r="F20" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="H20" s="10" t="s">
+        <v>27</v>
       </c>
       <c r="L20" s="2"/>
       <c r="N20" s="2"/>
@@ -1935,163 +2223,136 @@
       <c r="Y20" s="2"/>
       <c r="Z20" s="2"/>
     </row>
-    <row r="21" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A21" s="2">
-        <v>1</v>
-      </c>
-      <c r="B21" s="2" t="s">
+    <row r="21" spans="1:26" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="B21" s="22" t="s">
+        <v>101</v>
+      </c>
+      <c r="C21" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="D21" s="29">
+        <v>4</v>
+      </c>
+      <c r="E21" s="28">
+        <v>12</v>
+      </c>
+      <c r="F21" s="20"/>
+      <c r="H21" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="N21" s="25"/>
+    </row>
+    <row r="22" spans="1:26" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="14">
+        <v>1</v>
+      </c>
+      <c r="B22" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C22" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="D21" s="2">
-        <v>1</v>
-      </c>
-      <c r="E21" s="2">
-        <v>1</v>
-      </c>
-      <c r="F21" s="2" t="s">
+      <c r="D22" s="14">
+        <v>1</v>
+      </c>
+      <c r="E22" s="18">
+        <v>1</v>
+      </c>
+      <c r="F22" s="23" t="s">
         <v>89</v>
       </c>
-      <c r="H21" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="L21" s="2"/>
-      <c r="N21" s="2" t="s">
+      <c r="G22" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="H22" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="I22" s="14"/>
+      <c r="J22" s="14"/>
+      <c r="K22" s="14"/>
+      <c r="L22" s="14"/>
+      <c r="M22" s="14"/>
+      <c r="N22" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="O21" s="8" t="s">
+      <c r="O22" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="P21" s="8"/>
-      <c r="Q21" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="T21" s="2">
+      <c r="P22" s="18"/>
+      <c r="Q22" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="R22" s="14"/>
+      <c r="S22" s="14"/>
+      <c r="T22" s="14">
         <v>0</v>
       </c>
-      <c r="W21" s="2" t="s">
+      <c r="U22" s="14"/>
+      <c r="V22" s="14"/>
+      <c r="W22" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="X21" s="2" t="s">
+      <c r="X22" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="Y21" s="2"/>
-      <c r="Z21" s="2"/>
-    </row>
-    <row r="22" spans="1:26" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="8">
+      <c r="Y22" s="14"/>
+      <c r="Z22" s="14"/>
+    </row>
+    <row r="23" spans="1:26" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="2">
         <v>2</v>
       </c>
-      <c r="B22" s="8" t="s">
+      <c r="B23" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="C23" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D22" s="8">
-        <v>1</v>
-      </c>
-      <c r="E22" s="8">
+      <c r="D23" s="2">
+        <v>1</v>
+      </c>
+      <c r="E23" s="8">
         <v>2</v>
       </c>
-      <c r="F22" s="8" t="s">
+      <c r="F23" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="G22" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="H22" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="I22" s="8" t="s">
+      <c r="G23" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="H23" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="I23" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="J22" s="8"/>
-      <c r="K22" s="8" t="s">
+      <c r="J23" s="8"/>
+      <c r="K23" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="L22" s="8"/>
-      <c r="M22" s="8"/>
-      <c r="N22" s="8"/>
-      <c r="O22" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="P22" s="8"/>
-      <c r="Q22" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="R22" s="8">
-        <v>1</v>
-      </c>
-      <c r="S22" s="8"/>
-      <c r="T22" s="8">
-        <v>1</v>
-      </c>
-      <c r="U22" s="8">
-        <v>1</v>
-      </c>
-      <c r="V22" s="8"/>
-      <c r="W22" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="X22" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="Y22" s="8"/>
-      <c r="Z22" s="8"/>
-    </row>
-    <row r="23" spans="1:26" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="8">
-        <v>3</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="D23" s="8">
-        <v>1</v>
-      </c>
-      <c r="E23" s="8">
-        <v>3</v>
-      </c>
-      <c r="F23" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="G23" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="H23" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="I23" s="8"/>
-      <c r="J23" s="8"/>
-      <c r="K23" s="8"/>
       <c r="L23" s="8"/>
-      <c r="M23" s="8">
-        <v>1</v>
-      </c>
-      <c r="N23" s="8" t="s">
-        <v>69</v>
-      </c>
+      <c r="M23" s="8"/>
+      <c r="N23" s="8"/>
       <c r="O23" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="P23" s="8" t="s">
-        <v>74</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="P23" s="8"/>
       <c r="Q23" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="R23" s="8"/>
+      <c r="R23" s="8">
+        <v>1</v>
+      </c>
       <c r="S23" s="8"/>
       <c r="T23" s="8">
-        <v>0</v>
-      </c>
-      <c r="U23" s="8"/>
+        <v>1</v>
+      </c>
+      <c r="U23" s="8">
+        <v>1</v>
+      </c>
       <c r="V23" s="8"/>
       <c r="W23" s="8" t="s">
         <v>11</v>
@@ -2103,43 +2364,45 @@
       <c r="Z23" s="8"/>
     </row>
     <row r="24" spans="1:26" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="8">
-        <v>4</v>
-      </c>
-      <c r="B24" s="8" t="s">
+      <c r="A24" s="2">
+        <v>3</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="C24" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D24" s="8">
+      <c r="D24" s="2">
         <v>1</v>
       </c>
       <c r="E24" s="8">
-        <v>4</v>
-      </c>
-      <c r="F24" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="16" t="s">
         <v>89</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="H24" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="H24" s="10" t="s">
         <v>27</v>
       </c>
       <c r="I24" s="8"/>
       <c r="J24" s="8"/>
       <c r="K24" s="8"/>
       <c r="L24" s="8"/>
-      <c r="M24" s="8"/>
+      <c r="M24" s="8">
+        <v>1</v>
+      </c>
       <c r="N24" s="8" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="O24" s="8" t="s">
         <v>7</v>
       </c>
       <c r="P24" s="8" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="Q24" s="8" t="s">
         <v>8</v>
@@ -2161,122 +2424,124 @@
       <c r="Z24" s="8"/>
     </row>
     <row r="25" spans="1:26" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="8">
-        <v>5</v>
-      </c>
-      <c r="B25" s="8" t="s">
+      <c r="A25" s="2">
+        <v>4</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="C25" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D25" s="8">
-        <v>1</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="F25" s="8" t="s">
+      <c r="D25" s="2">
+        <v>1</v>
+      </c>
+      <c r="E25" s="8">
+        <v>4</v>
+      </c>
+      <c r="F25" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="G25" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="H25" s="8" t="s">
-        <v>23</v>
+      <c r="G25" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="H25" s="10" t="s">
+        <v>27</v>
       </c>
       <c r="I25" s="8"/>
-      <c r="J25" s="8" t="s">
-        <v>33</v>
-      </c>
+      <c r="J25" s="8"/>
       <c r="K25" s="8"/>
       <c r="L25" s="8"/>
       <c r="M25" s="8"/>
-      <c r="N25" s="8"/>
+      <c r="N25" s="8" t="s">
+        <v>86</v>
+      </c>
       <c r="O25" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="P25" s="8"/>
+        <v>7</v>
+      </c>
+      <c r="P25" s="8" t="s">
+        <v>64</v>
+      </c>
       <c r="Q25" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="R25" s="8">
-        <v>1</v>
-      </c>
+      <c r="R25" s="8"/>
       <c r="S25" s="8"/>
       <c r="T25" s="8">
-        <v>1</v>
-      </c>
-      <c r="U25" s="8">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U25" s="8"/>
       <c r="V25" s="8"/>
       <c r="W25" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="X25" s="8"/>
+      <c r="X25" s="8" t="s">
+        <v>18</v>
+      </c>
       <c r="Y25" s="8"/>
       <c r="Z25" s="8"/>
     </row>
-    <row r="26" spans="1:26" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:26" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D26" s="2">
-        <v>2</v>
-      </c>
-      <c r="E26" s="2">
-        <v>5</v>
-      </c>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I26" s="2"/>
-      <c r="J26" s="2"/>
-      <c r="K26" s="2"/>
-      <c r="L26" s="2">
-        <v>1</v>
-      </c>
-      <c r="M26" s="2"/>
-      <c r="N26" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F26" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="H26" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="I26" s="8"/>
+      <c r="J26" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="K26" s="8"/>
+      <c r="L26" s="8"/>
+      <c r="M26" s="8"/>
+      <c r="N26" s="8"/>
       <c r="O26" s="8" t="s">
         <v>8</v>
       </c>
       <c r="P26" s="8"/>
       <c r="Q26" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="R26" s="4">
-        <v>4</v>
-      </c>
-      <c r="S26" s="4"/>
-      <c r="T26" s="4">
-        <v>2</v>
-      </c>
-      <c r="U26" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="V26" s="4"/>
-      <c r="W26" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="X26" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="Y26" s="4"/>
-      <c r="Z26" s="4"/>
-    </row>
-    <row r="27" spans="1:26" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="R26" s="8">
+        <v>1</v>
+      </c>
+      <c r="S26" s="8"/>
+      <c r="T26" s="8">
+        <v>1</v>
+      </c>
+      <c r="U26" s="8">
+        <v>1</v>
+      </c>
+      <c r="V26" s="8"/>
+      <c r="W26" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="X26" s="8"/>
+      <c r="Y26" s="8"/>
+      <c r="Z26" s="8"/>
+    </row>
+    <row r="27" spans="1:26" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>34</v>
@@ -2287,43 +2552,52 @@
       <c r="D27" s="2">
         <v>2</v>
       </c>
-      <c r="E27" s="2">
+      <c r="E27" s="8">
         <v>5</v>
       </c>
-      <c r="F27" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="H27" s="2" t="s">
+      <c r="F27" s="13"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="I27" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="L27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+      <c r="K27" s="2"/>
+      <c r="L27" s="2">
+        <v>1</v>
+      </c>
+      <c r="M27" s="2"/>
       <c r="N27" s="2"/>
       <c r="O27" s="8" t="s">
         <v>8</v>
       </c>
       <c r="P27" s="8"/>
       <c r="Q27" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="T27" s="2">
-        <v>0</v>
-      </c>
-      <c r="W27" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="X27" s="2"/>
-      <c r="Y27" s="2"/>
-      <c r="Z27" s="2"/>
+        <v>7</v>
+      </c>
+      <c r="R27" s="8">
+        <v>4</v>
+      </c>
+      <c r="S27" s="8"/>
+      <c r="T27" s="8">
+        <v>2</v>
+      </c>
+      <c r="U27" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="V27" s="8"/>
+      <c r="W27" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="X27" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y27" s="4"/>
+      <c r="Z27" s="4"/>
     </row>
     <row r="28" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>34</v>
@@ -2334,52 +2608,46 @@
       <c r="D28" s="2">
         <v>2</v>
       </c>
-      <c r="E28" s="2">
-        <v>6</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>27</v>
+      <c r="E28" s="8">
+        <v>5</v>
+      </c>
+      <c r="F28" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="H28" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>96</v>
       </c>
       <c r="L28" s="2"/>
-      <c r="M28" s="2">
-        <v>3</v>
-      </c>
-      <c r="N28" s="2">
-        <v>1</v>
-      </c>
+      <c r="N28" s="2"/>
       <c r="O28" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="P28" s="8" t="s">
-        <v>37</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="P28" s="8"/>
       <c r="Q28" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="S28" s="2">
-        <v>1</v>
-      </c>
       <c r="T28" s="2">
-        <v>1</v>
-      </c>
-      <c r="U28" s="2" t="s">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="W28" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="X28" s="8" t="s">
-        <v>24</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="X28" s="2"/>
       <c r="Y28" s="2"/>
       <c r="Z28" s="2"/>
     </row>
     <row r="29" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>34</v>
@@ -2390,50 +2658,55 @@
       <c r="D29" s="2">
         <v>2</v>
       </c>
-      <c r="E29" s="2">
-        <v>7</v>
-      </c>
-      <c r="F29" s="2" t="s">
+      <c r="E29" s="8">
+        <v>6</v>
+      </c>
+      <c r="F29" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="H29" s="2" t="s">
+      <c r="G29" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H29" s="10" t="s">
         <v>27</v>
       </c>
       <c r="L29" s="2"/>
       <c r="M29" s="2">
-        <v>2</v>
-      </c>
-      <c r="N29" s="2" t="s">
-        <v>69</v>
+        <v>3</v>
+      </c>
+      <c r="N29" s="2">
+        <v>1</v>
       </c>
       <c r="O29" s="8" t="s">
         <v>7</v>
       </c>
       <c r="P29" s="8" t="s">
-        <v>74</v>
+        <v>37</v>
       </c>
       <c r="Q29" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="S29" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="T29" s="2" t="s">
-        <v>27</v>
+      <c r="S29" s="2">
+        <v>1</v>
+      </c>
+      <c r="T29" s="2">
+        <v>1</v>
       </c>
       <c r="U29" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="W29" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="X29" s="8"/>
+        <v>12</v>
+      </c>
+      <c r="X29" s="8" t="s">
+        <v>24</v>
+      </c>
       <c r="Y29" s="2"/>
       <c r="Z29" s="2"/>
     </row>
     <row r="30" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>34</v>
@@ -2444,108 +2717,111 @@
       <c r="D30" s="2">
         <v>2</v>
       </c>
-      <c r="E30" s="2">
-        <v>8</v>
-      </c>
-      <c r="F30" s="2" t="s">
+      <c r="E30" s="8">
+        <v>7</v>
+      </c>
+      <c r="F30" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="H30" s="2" t="s">
-        <v>23</v>
+      <c r="G30" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H30" s="10" t="s">
+        <v>27</v>
       </c>
       <c r="L30" s="2"/>
       <c r="M30" s="2">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="O30" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="P30" s="8"/>
+      <c r="P30" s="8" t="s">
+        <v>74</v>
+      </c>
       <c r="Q30" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="R30" s="2">
-        <v>1</v>
-      </c>
       <c r="S30" s="2" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="T30" s="2" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="U30" s="2" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="W30" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="X30" s="8" t="s">
-        <v>81</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="X30" s="8"/>
       <c r="Y30" s="2"/>
       <c r="Z30" s="2"/>
     </row>
     <row r="31" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D31" s="2">
-        <v>3</v>
-      </c>
-      <c r="E31" s="2">
-        <v>9</v>
-      </c>
-      <c r="F31" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E31" s="8">
+        <v>8</v>
+      </c>
+      <c r="F31" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="H31" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J31" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K31" s="2" t="s">
-        <v>92</v>
+      <c r="G31" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H31" s="10" t="s">
+        <v>27</v>
       </c>
       <c r="L31" s="2"/>
-      <c r="N31" s="2"/>
+      <c r="M31" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N31" s="2" t="s">
+        <v>69</v>
+      </c>
       <c r="O31" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="P31" s="8"/>
+        <v>7</v>
+      </c>
+      <c r="P31" s="8" t="s">
+        <v>75</v>
+      </c>
       <c r="Q31" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="T31" s="2">
-        <v>0</v>
+      <c r="S31" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="T31" s="8" t="s">
+        <v>27</v>
       </c>
       <c r="U31" s="2" t="s">
-        <v>27</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="V31" s="3"/>
       <c r="W31" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="X31" s="8" t="s">
-        <v>18</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="X31" s="8"/>
       <c r="Y31" s="2"/>
       <c r="Z31" s="2"/>
     </row>
     <row r="32" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>38</v>
@@ -2556,51 +2832,48 @@
       <c r="D32" s="2">
         <v>3</v>
       </c>
-      <c r="E32" s="2">
+      <c r="E32" s="8">
+        <v>9</v>
+      </c>
+      <c r="F32" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="H32" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="L32" s="2"/>
+      <c r="N32" s="2"/>
+      <c r="O32" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="P32" s="8"/>
+      <c r="Q32" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="T32" s="2">
+        <v>0</v>
+      </c>
+      <c r="U32" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="W32" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F32" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="L32" s="2"/>
-      <c r="M32" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="N32" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="O32" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="P32" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q32" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="S32" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="T32" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="U32" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="V32" s="3"/>
-      <c r="W32" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="X32" s="8"/>
+      <c r="X32" s="8" t="s">
+        <v>18</v>
+      </c>
       <c r="Y32" s="2"/>
       <c r="Z32" s="2"/>
     </row>
     <row r="33" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>38</v>
@@ -2611,97 +2884,107 @@
       <c r="D33" s="2">
         <v>3</v>
       </c>
-      <c r="E33" s="2">
-        <v>11</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>91</v>
+      <c r="E33" s="8">
+        <v>10</v>
+      </c>
+      <c r="F33" s="13" t="s">
+        <v>89</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="I33" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H33" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="L33" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="N33" s="2"/>
+      <c r="L33" s="2"/>
+      <c r="M33" s="2">
+        <v>3.1</v>
+      </c>
+      <c r="N33" s="2" t="s">
+        <v>71</v>
+      </c>
       <c r="O33" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="P33" s="8"/>
+        <v>7</v>
+      </c>
+      <c r="P33" s="2" t="s">
+        <v>99</v>
+      </c>
       <c r="Q33" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="T33" s="2">
-        <v>0</v>
-      </c>
-      <c r="W33" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="X33" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="Y33" s="2"/>
-      <c r="Z33" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="R33" s="2">
+        <v>1</v>
+      </c>
+      <c r="S33" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="T33" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="U33" s="2" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="34" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D34" s="2">
-        <v>4</v>
-      </c>
-      <c r="E34" s="2">
-        <v>12</v>
-      </c>
-      <c r="F34" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E34" s="8">
+        <v>11</v>
+      </c>
+      <c r="F34" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="H34" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="L34" s="2"/>
+      <c r="G34" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H34" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="K34" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="L34" s="2" t="s">
+        <v>23</v>
+      </c>
       <c r="N34" s="2"/>
       <c r="O34" s="8" t="s">
         <v>8</v>
       </c>
       <c r="P34" s="8"/>
       <c r="Q34" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="R34" s="2" t="s">
-        <v>58</v>
+        <v>7</v>
       </c>
       <c r="T34" s="2">
         <v>0</v>
       </c>
-      <c r="U34" s="2">
-        <v>1</v>
-      </c>
       <c r="W34" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="X34" s="8"/>
+        <v>11</v>
+      </c>
+      <c r="X34" s="8" t="s">
+        <v>24</v>
+      </c>
       <c r="Y34" s="2"/>
       <c r="Z34" s="2"/>
     </row>
     <row r="35" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>31</v>
@@ -2709,17 +2992,17 @@
       <c r="D35" s="2">
         <v>4</v>
       </c>
-      <c r="E35" s="2">
-        <v>13</v>
-      </c>
-      <c r="F35" s="2" t="s">
+      <c r="E35" s="8">
+        <v>12</v>
+      </c>
+      <c r="F35" s="13" t="s">
         <v>89</v>
       </c>
+      <c r="G35" s="2" t="s">
+        <v>95</v>
+      </c>
       <c r="H35" s="2" t="s">
         <v>27</v>
-      </c>
-      <c r="J35" s="2" t="s">
-        <v>43</v>
       </c>
       <c r="L35" s="2"/>
       <c r="N35" s="2"/>
@@ -2730,14 +3013,17 @@
       <c r="Q35" s="8" t="s">
         <v>8</v>
       </c>
+      <c r="R35" s="2" t="s">
+        <v>58</v>
+      </c>
       <c r="T35" s="2">
-        <v>1</v>
-      </c>
-      <c r="U35" s="2" t="s">
-        <v>27</v>
+        <v>0</v>
+      </c>
+      <c r="U35" s="2">
+        <v>1</v>
       </c>
       <c r="W35" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="X35" s="8"/>
       <c r="Y35" s="2"/>
@@ -2745,10 +3031,10 @@
     </row>
     <row r="36" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>31</v>
@@ -2756,36 +3042,32 @@
       <c r="D36" s="2">
         <v>4</v>
       </c>
-      <c r="E36" s="2">
-        <v>14</v>
-      </c>
-      <c r="F36" s="2" t="s">
+      <c r="E36" s="8">
+        <v>13</v>
+      </c>
+      <c r="F36" s="13" t="s">
         <v>89</v>
       </c>
+      <c r="G36" s="2" t="s">
+        <v>95</v>
+      </c>
       <c r="H36" s="2" t="s">
         <v>27</v>
       </c>
+      <c r="J36" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="L36" s="2"/>
-      <c r="M36" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N36" s="2" t="s">
-        <v>69</v>
-      </c>
+      <c r="N36" s="2"/>
       <c r="O36" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="P36" s="8" t="s">
-        <v>73</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="P36" s="8"/>
       <c r="Q36" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="S36" s="2">
-        <v>4</v>
-      </c>
       <c r="T36" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U36" s="2" t="s">
         <v>27</v>
@@ -2799,42 +3081,50 @@
     </row>
     <row r="37" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D37" s="2">
-        <v>5</v>
-      </c>
-      <c r="E37" s="2">
-        <v>13</v>
-      </c>
-      <c r="F37" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E37" s="8">
+        <v>14</v>
+      </c>
+      <c r="F37" s="13" t="s">
         <v>89</v>
       </c>
+      <c r="G37" s="2" t="s">
+        <v>95</v>
+      </c>
       <c r="H37" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="J37" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="L37" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="N37" s="2"/>
+      <c r="L37" s="2"/>
+      <c r="M37" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N37" s="2" t="s">
+        <v>69</v>
+      </c>
       <c r="O37" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="P37" s="8"/>
+        <v>7</v>
+      </c>
+      <c r="P37" s="8" t="s">
+        <v>73</v>
+      </c>
       <c r="Q37" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="T37" s="8">
-        <v>1</v>
+        <v>8</v>
+      </c>
+      <c r="S37" s="2">
+        <v>4</v>
+      </c>
+      <c r="T37" s="2">
+        <v>2</v>
       </c>
       <c r="U37" s="2" t="s">
         <v>27</v>
@@ -2842,18 +3132,16 @@
       <c r="W37" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="X37" s="8" t="s">
-        <v>24</v>
-      </c>
+      <c r="X37" s="8"/>
       <c r="Y37" s="2"/>
       <c r="Z37" s="2"/>
     </row>
     <row r="38" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A38" s="2">
-        <v>18</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>46</v>
+      <c r="A38" s="8">
+        <v>17</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>44</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>31</v>
@@ -2861,42 +3149,53 @@
       <c r="D38" s="2">
         <v>5</v>
       </c>
-      <c r="E38" s="2">
+      <c r="E38" s="8">
         <v>13</v>
       </c>
+      <c r="F38" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>95</v>
+      </c>
       <c r="H38" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="L38" s="2"/>
+      <c r="J38" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="L38" s="2" t="s">
+        <v>23</v>
+      </c>
       <c r="N38" s="2"/>
       <c r="O38" s="8" t="s">
         <v>8</v>
       </c>
       <c r="P38" s="8"/>
       <c r="Q38" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="T38" s="2">
-        <v>0</v>
+        <v>7</v>
+      </c>
+      <c r="T38" s="8">
+        <v>1</v>
       </c>
       <c r="U38" s="2" t="s">
         <v>27</v>
       </c>
       <c r="W38" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="X38" s="8" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="Y38" s="2"/>
       <c r="Z38" s="2"/>
     </row>
     <row r="39" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A39" s="2">
-        <v>19</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>47</v>
+      <c r="A39" s="8">
+        <v>18</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>46</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>31</v>
@@ -2904,82 +3203,133 @@
       <c r="D39" s="2">
         <v>5</v>
       </c>
-      <c r="E39" s="2">
-        <v>15</v>
-      </c>
+      <c r="E39" s="27">
+        <v>13</v>
+      </c>
+      <c r="F39" s="13"/>
       <c r="H39" s="2" t="s">
         <v>27</v>
       </c>
       <c r="L39" s="2"/>
-      <c r="N39" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="O39" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="P39" s="2"/>
-      <c r="Q39" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="S39" s="3">
-        <v>3</v>
+      <c r="N39" s="2"/>
+      <c r="O39" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="P39" s="8"/>
+      <c r="Q39" s="8" t="s">
+        <v>8</v>
       </c>
       <c r="T39" s="2">
         <v>0</v>
       </c>
-      <c r="U39" s="2">
-        <v>1</v>
+      <c r="U39" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="W39" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="X39" s="8"/>
+      <c r="X39" s="8" t="s">
+        <v>18</v>
+      </c>
       <c r="Y39" s="2"/>
       <c r="Z39" s="2"/>
     </row>
     <row r="40" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="D40" s="1"/>
-      <c r="E40" s="1"/>
-      <c r="F40" s="1"/>
-      <c r="G40" s="1"/>
-      <c r="H40" s="1"/>
-      <c r="I40" s="1"/>
-      <c r="J40" s="1"/>
-      <c r="K40" s="1"/>
-      <c r="M40" s="1"/>
-      <c r="N40" s="1"/>
-      <c r="X40" s="7"/>
-    </row>
-    <row r="41" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="D41" s="1"/>
-      <c r="E41" s="1"/>
-      <c r="F41" s="1"/>
-      <c r="G41" s="1"/>
-      <c r="H41" s="1"/>
-      <c r="I41" s="1"/>
-      <c r="J41" s="1"/>
-      <c r="K41" s="1"/>
-      <c r="M41" s="1"/>
-      <c r="N41" s="1"/>
-      <c r="X41" s="7"/>
-    </row>
-    <row r="42" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="D42" s="1"/>
-      <c r="E42" s="1"/>
-      <c r="F42" s="1"/>
-      <c r="G42" s="1"/>
-      <c r="H42" s="1"/>
-      <c r="I42" s="1"/>
-      <c r="J42" s="1"/>
-      <c r="K42" s="1"/>
-      <c r="M42" s="1"/>
-      <c r="N42" s="1"/>
-      <c r="X42" s="7"/>
+      <c r="A40" s="8">
+        <v>19</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D40" s="2">
+        <v>5</v>
+      </c>
+      <c r="E40" s="27">
+        <v>15</v>
+      </c>
+      <c r="F40" s="13"/>
+      <c r="H40" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L40" s="2"/>
+      <c r="N40" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="O40" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="P40" s="2"/>
+      <c r="Q40" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S40" s="3">
+        <v>3</v>
+      </c>
+      <c r="T40" s="2">
+        <v>0</v>
+      </c>
+      <c r="U40" s="2">
+        <v>1</v>
+      </c>
+      <c r="W40" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="X40" s="8"/>
+      <c r="Y40" s="2"/>
+      <c r="Z40" s="2"/>
+    </row>
+    <row r="41" spans="1:26" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="B41" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="C41" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="D41" s="29">
+        <v>4</v>
+      </c>
+      <c r="E41" s="28">
+        <v>14</v>
+      </c>
+      <c r="F41" s="20"/>
+      <c r="H41" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="X41" s="22"/>
+    </row>
+    <row r="42" spans="1:26" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F42" s="14"/>
+      <c r="G42" s="14"/>
+      <c r="H42" s="14"/>
+      <c r="I42" s="14"/>
+      <c r="J42" s="14"/>
+      <c r="K42" s="14"/>
+      <c r="M42" s="14"/>
+      <c r="N42" s="17"/>
+      <c r="R42" s="14"/>
+      <c r="S42" s="14"/>
+      <c r="T42" s="14"/>
+      <c r="U42" s="14"/>
+      <c r="V42" s="14"/>
+      <c r="W42" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="X42" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="Y42" s="14"/>
+      <c r="Z42" s="14"/>
     </row>
     <row r="43" spans="1:26" x14ac:dyDescent="0.25">
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
-      <c r="F43" s="1"/>
+      <c r="F43" s="12"/>
       <c r="G43" s="1"/>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
@@ -2992,7 +3342,7 @@
     <row r="44" spans="1:26" x14ac:dyDescent="0.25">
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
-      <c r="F44" s="1"/>
+      <c r="F44" s="12"/>
       <c r="G44" s="1"/>
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
@@ -3004,7 +3354,7 @@
     <row r="45" spans="1:26" x14ac:dyDescent="0.25">
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
-      <c r="F45" s="1"/>
+      <c r="F45" s="12"/>
       <c r="G45" s="1"/>
       <c r="H45" s="1"/>
       <c r="I45" s="1"/>
@@ -3016,7 +3366,7 @@
     <row r="46" spans="1:26" x14ac:dyDescent="0.25">
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
-      <c r="F46" s="1"/>
+      <c r="F46" s="12"/>
       <c r="G46" s="1"/>
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
@@ -3650,9 +4000,10 @@
       <c r="N98" s="1"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B21:X39">
-    <sortCondition ref="D21:D39"/>
-    <sortCondition ref="E21:E39"/>
+  <autoFilter ref="A1:Z98" xr:uid="{E5603586-01B1-45C3-888E-EC2BF5D85650}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B22:X40">
+    <sortCondition ref="D22:D40"/>
+    <sortCondition ref="E22:E40"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
